--- a/public/exports/29189927.xlsx
+++ b/public/exports/29189927.xlsx
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">342884, 342886</t>
+          <t xml:space="preserve">342475</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F16">
-        <v>10411</v>
+        <v>1027</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4461243</t>
+          <t xml:space="preserve">342884, 342886</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F17">
-        <v>1870</v>
+        <v>10411</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -886,11 +886,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F18">
-        <v>1747</v>
+        <v>1870</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4461367</t>
+          <t xml:space="preserve">4461243</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F19">
-        <v>420</v>
+        <v>1747</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4461539</t>
+          <t xml:space="preserve">4461367</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F20">
-        <v>286</v>
+        <v>420</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4488794</t>
+          <t xml:space="preserve">4461539</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F21">
-        <v>1678</v>
+        <v>286</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4493849</t>
+          <t xml:space="preserve">4488794</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F22">
-        <v>4767</v>
+        <v>1678</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1136,11 +1136,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F23">
-        <v>2749</v>
+        <v>4767</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1186,11 +1186,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F24">
-        <v>2067</v>
+        <v>2749</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">4495667</t>
+          <t xml:space="preserve">4493849</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F25">
-        <v>1089</v>
+        <v>2067</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">4495687</t>
+          <t xml:space="preserve">4495667</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F26">
-        <v>790</v>
+        <v>1089</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4498461</t>
+          <t xml:space="preserve">4495687</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="F27">
-        <v>849</v>
+        <v>790</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4503816</t>
+          <t xml:space="preserve">4498461</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F28">
-        <v>549</v>
+        <v>849</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1436,11 +1436,11 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F29">
-        <v>305</v>
+        <v>549</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1486,11 +1486,11 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F30">
-        <v>2341</v>
+        <v>305</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1531,16 +1531,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4504175</t>
+          <t xml:space="preserve">4503816</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F31">
-        <v>1763</v>
+        <v>2341</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1586,11 +1586,11 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F32">
-        <v>2601</v>
+        <v>1763</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1636,11 +1636,11 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F33">
-        <v>398</v>
+        <v>2601</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1681,16 +1681,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">4504311</t>
+          <t xml:space="preserve">4504175</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F34">
-        <v>813</v>
+        <v>398</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2281,16 +2281,16 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5710842</t>
+          <t xml:space="preserve">5712180</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F46">
-        <v>1063</v>
+        <v>4028</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2331,16 +2331,16 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5712180</t>
+          <t xml:space="preserve">5712186</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F47">
-        <v>4028</v>
+        <v>600</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2386,11 +2386,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F48">
-        <v>600</v>
+        <v>2395</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2431,16 +2431,16 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5712186</t>
+          <t xml:space="preserve">5713126</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F49">
-        <v>2395</v>
+        <v>379</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5713126</t>
+          <t xml:space="preserve">5713665</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="F50">
-        <v>379</v>
+        <v>462</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5713665</t>
+          <t xml:space="preserve">5714270</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="F51">
-        <v>462</v>
+        <v>406</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5714270</t>
+          <t xml:space="preserve">5716420</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="F52">
-        <v>406</v>
+        <v>610</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2631,16 +2631,16 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716411</t>
+          <t xml:space="preserve">5716420</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F53">
-        <v>440</v>
+        <v>257</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2681,16 +2681,16 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716420</t>
+          <t xml:space="preserve">5716802</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F54">
-        <v>610</v>
+        <v>260</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716420</t>
+          <t xml:space="preserve">5716944</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="F55">
-        <v>257</v>
+        <v>319</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716802</t>
+          <t xml:space="preserve">5716944</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="F56">
-        <v>260</v>
+        <v>319</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2836,11 +2836,11 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F57">
-        <v>319</v>
+        <v>271</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,11 +2886,11 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F58">
-        <v>319</v>
+        <v>689</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2931,16 +2931,16 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716944</t>
+          <t xml:space="preserve">5719403</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F59">
-        <v>271</v>
+        <v>4675</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2981,16 +2981,16 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716944</t>
+          <t xml:space="preserve">5719403</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F60">
-        <v>689</v>
+        <v>1611</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3036,11 +3036,11 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F61">
-        <v>4675</v>
+        <v>944</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3086,11 +3086,11 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F62">
-        <v>1611</v>
+        <v>1156</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3136,11 +3136,11 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F63">
-        <v>944</v>
+        <v>370</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3181,16 +3181,16 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5719403</t>
+          <t xml:space="preserve">7006806</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F64">
-        <v>1156</v>
+        <v>3174</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3231,16 +3231,16 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5719403</t>
+          <t xml:space="preserve">7006806</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F65">
-        <v>370</v>
+        <v>410</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3286,11 +3286,11 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F66">
-        <v>3174</v>
+        <v>8453</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3336,11 +3336,11 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F67">
-        <v>410</v>
+        <v>6981</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3381,16 +3381,16 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">7006806</t>
+          <t xml:space="preserve">740184, 9800976</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F68">
-        <v>8453</v>
+        <v>1716</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3431,16 +3431,16 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">7006806</t>
+          <t xml:space="preserve">740244, 4493996</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F69">
-        <v>6981</v>
+        <v>1500</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3481,16 +3481,16 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">740181, 5000804</t>
+          <t xml:space="preserve">740244, 4493996</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F70">
-        <v>556</v>
+        <v>1152</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3531,16 +3531,16 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">740181, 5000804</t>
+          <t xml:space="preserve">740247, 5712933</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F71">
-        <v>285</v>
+        <v>900</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">740184, 9800976</t>
+          <t xml:space="preserve">740248, 5712934</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3590,7 +3590,7 @@
         </is>
       </c>
       <c r="F72">
-        <v>1716</v>
+        <v>366</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">740239, 5710277</t>
+          <t xml:space="preserve">740250, 4498461</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="F73">
-        <v>541</v>
+        <v>2606</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3681,16 +3681,16 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">740239, 5710277</t>
+          <t xml:space="preserve">740254, 4493934</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F74">
-        <v>794</v>
+        <v>388</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">740244, 4493996</t>
+          <t xml:space="preserve">740256, 7190859</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="F75">
-        <v>1500</v>
+        <v>1014</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3781,16 +3781,16 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">740244, 4493996</t>
+          <t xml:space="preserve">740258, 4488794</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F76">
-        <v>1152</v>
+        <v>1845</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3831,16 +3831,16 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">740247, 5712933</t>
+          <t xml:space="preserve">740258, 4488794</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F77">
-        <v>900</v>
+        <v>1635</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">740248, 5712934</t>
+          <t xml:space="preserve">740260, 4495015</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="F78">
-        <v>366</v>
+        <v>2002</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3931,16 +3931,16 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">740250, 4498461</t>
+          <t xml:space="preserve">740261, 5716124</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F79">
-        <v>2606</v>
+        <v>254</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3981,16 +3981,16 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">740254, 4493934</t>
+          <t xml:space="preserve">740262, 9447609</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F80">
-        <v>388</v>
+        <v>3010</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4031,16 +4031,16 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">740256, 7190859</t>
+          <t xml:space="preserve">740268, 4461539</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F81">
-        <v>1014</v>
+        <v>2916</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4081,16 +4081,16 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">740258, 4488794</t>
+          <t xml:space="preserve">740582, 1510489</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F82">
-        <v>1845</v>
+        <v>300</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4131,16 +4131,16 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">740258, 4488794</t>
+          <t xml:space="preserve">740586, 9777442</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F83">
-        <v>1635</v>
+        <v>1942</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4181,16 +4181,16 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">740260, 4495015</t>
+          <t xml:space="preserve">740586, 9777442</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F84">
-        <v>2002</v>
+        <v>541</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4231,16 +4231,16 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">740261, 5716124</t>
+          <t xml:space="preserve">740586, 9777442</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F85">
-        <v>254</v>
+        <v>1403</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4281,16 +4281,16 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">740262, 9447609</t>
+          <t xml:space="preserve">740586, 9777442</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F86">
-        <v>3010</v>
+        <v>851</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4331,16 +4331,16 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">740268, 4461539</t>
+          <t xml:space="preserve">740587, 7030832</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F87">
-        <v>2916</v>
+        <v>378</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4381,16 +4381,16 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">740582, 1510489</t>
+          <t xml:space="preserve">740587, 7030832</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F88">
-        <v>300</v>
+        <v>391</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4431,16 +4431,16 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">740586, 9777442</t>
+          <t xml:space="preserve">740587, 7030832</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F89">
-        <v>1942</v>
+        <v>1953</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4481,16 +4481,16 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">740586, 9777442</t>
+          <t xml:space="preserve">740592, 5719480</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F90">
-        <v>541</v>
+        <v>1348</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4531,16 +4531,16 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">740586, 9777442</t>
+          <t xml:space="preserve">740662, 4501291</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="F91">
-        <v>1403</v>
+        <v>548</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -4581,16 +4581,16 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">740586, 9777442</t>
+          <t xml:space="preserve">740664, 4501285</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F92">
-        <v>851</v>
+        <v>317</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -4631,16 +4631,16 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">740587, 7030832</t>
+          <t xml:space="preserve">740669, 4501292</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">49</t>
         </is>
       </c>
       <c r="F93">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -4681,16 +4681,16 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">740587, 7030832</t>
+          <t xml:space="preserve">740736, 4514043</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F94">
-        <v>391</v>
+        <v>487</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -4731,16 +4731,16 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">740587, 7030832</t>
+          <t xml:space="preserve">740737, 4507216</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F95">
-        <v>1953</v>
+        <v>2032</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">740592, 5719480</t>
+          <t xml:space="preserve">7900891</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="F96">
-        <v>1348</v>
+        <v>3989</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4831,16 +4831,16 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">740626, 8875947</t>
+          <t xml:space="preserve">8095136</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F97">
-        <v>293</v>
+        <v>673</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4881,16 +4881,16 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">740662, 4501291</t>
+          <t xml:space="preserve">8269227</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F98">
-        <v>548</v>
+        <v>316</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4931,16 +4931,16 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">740664, 4501285</t>
+          <t xml:space="preserve">8342484</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F99">
-        <v>317</v>
+        <v>670</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4981,16 +4981,16 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">740669, 4501292</t>
+          <t xml:space="preserve">8342484</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">49</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F100">
-        <v>390</v>
+        <v>670</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -5031,16 +5031,16 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">740736, 4514043</t>
+          <t xml:space="preserve">8342484</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F101">
-        <v>487</v>
+        <v>670</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -5081,16 +5081,16 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">740737, 4507216</t>
+          <t xml:space="preserve">8342484</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F102">
-        <v>2032</v>
+        <v>670</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -5131,16 +5131,16 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900891</t>
+          <t xml:space="preserve">8342484</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F103">
-        <v>3989</v>
+        <v>670</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -5176,12 +5176,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">661</t>
+          <t xml:space="preserve">671</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">8095136</t>
+          <t xml:space="preserve">8475859</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="F104">
-        <v>673</v>
+        <v>275</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -5231,16 +5231,16 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">8269227</t>
+          <t xml:space="preserve">8491428</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F105">
-        <v>316</v>
+        <v>729</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -5281,16 +5281,16 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">8342484</t>
+          <t xml:space="preserve">8491428</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F106">
-        <v>670</v>
+        <v>290</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5331,16 +5331,16 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">8342484</t>
+          <t xml:space="preserve">8630943</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F107">
-        <v>670</v>
+        <v>293</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -5381,16 +5381,16 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">8342484</t>
+          <t xml:space="preserve">8672254</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F108">
-        <v>670</v>
+        <v>286</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -5431,16 +5431,16 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">8342484</t>
+          <t xml:space="preserve">8672254, 100331202</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F109">
-        <v>670</v>
+        <v>1570</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">8342484</t>
+          <t xml:space="preserve">8981629</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F110">
-        <v>670</v>
+        <v>630</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -5526,21 +5526,21 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">671</t>
+          <t xml:space="preserve">661</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8475859</t>
+          <t xml:space="preserve">9123977</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F111">
-        <v>275</v>
+        <v>338</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -5581,16 +5581,16 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">8491428</t>
+          <t xml:space="preserve">9123977</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F112">
-        <v>729</v>
+        <v>284</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -5631,16 +5631,16 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">8491428</t>
+          <t xml:space="preserve">9123977</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F113">
-        <v>290</v>
+        <v>444</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -5681,16 +5681,16 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">8630943</t>
+          <t xml:space="preserve">9123977</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F114">
-        <v>293</v>
+        <v>638</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -5731,16 +5731,16 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">8672254</t>
+          <t xml:space="preserve">9389974</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F115">
-        <v>286</v>
+        <v>497</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -5781,16 +5781,16 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">8672254, 100331202</t>
+          <t xml:space="preserve">9389974</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F116">
-        <v>1570</v>
+        <v>320</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -5831,16 +5831,16 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">8875947</t>
+          <t xml:space="preserve">9413823</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F117">
-        <v>1968</v>
+        <v>640</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">8981629</t>
+          <t xml:space="preserve">9447916</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="F118">
-        <v>630</v>
+        <v>1312</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -5931,16 +5931,16 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123977</t>
+          <t xml:space="preserve">9447925</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F119">
-        <v>338</v>
+        <v>367</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -5981,16 +5981,16 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123977</t>
+          <t xml:space="preserve">9733938</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F120">
-        <v>284</v>
+        <v>399</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -6031,16 +6031,16 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123977</t>
+          <t xml:space="preserve">9745128</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F121">
-        <v>444</v>
+        <v>1025</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -6081,16 +6081,16 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123977</t>
+          <t xml:space="preserve">9777442</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F122">
-        <v>638</v>
+        <v>1275</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -6131,16 +6131,16 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9389974</t>
+          <t xml:space="preserve">9992464</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F123">
-        <v>497</v>
+        <v>653</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -6181,30 +6181,30 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9389974</t>
+          <t xml:space="preserve">4512452</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F124">
-        <v>320</v>
+        <v>285</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200013352</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-05-06</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9413823</t>
+          <t xml:space="preserve">4503820</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6240,21 +6240,21 @@
         </is>
       </c>
       <c r="F125">
-        <v>640</v>
+        <v>665</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200023605</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-11-09</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9447916</t>
+          <t xml:space="preserve">5716944</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6290,21 +6290,21 @@
         </is>
       </c>
       <c r="F126">
-        <v>1312</v>
+        <v>391</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200023681</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-11-10</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -6331,30 +6331,30 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9447925</t>
+          <t xml:space="preserve">7070788</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F127">
-        <v>367</v>
+        <v>455</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200023991</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-11-16</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -6381,30 +6381,30 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9447964</t>
+          <t xml:space="preserve">5716419</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F128">
-        <v>556</v>
+        <v>399</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200024698</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-11-28</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9733938</t>
+          <t xml:space="preserve">1475000</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -6440,21 +6440,21 @@
         </is>
       </c>
       <c r="F129">
-        <v>399</v>
+        <v>316</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200025346</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-12-11</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -6481,30 +6481,30 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">9745128</t>
+          <t xml:space="preserve">1475000</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F130">
-        <v>1025</v>
+        <v>347</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200025346</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-12-11</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -6531,30 +6531,30 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">9777442</t>
+          <t xml:space="preserve">5709252</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F131">
-        <v>1275</v>
+        <v>845</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200025544</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-12-16</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -6581,30 +6581,30 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">9992464</t>
+          <t xml:space="preserve">4494935</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F132">
-        <v>653</v>
+        <v>2185</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026093</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -6631,25 +6631,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">4512452</t>
+          <t xml:space="preserve">4494935</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F133">
-        <v>285</v>
+        <v>659</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">200013352</t>
+          <t xml:space="preserve">200026092</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-06</t>
+          <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">4503820</t>
+          <t xml:space="preserve">7727184</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6690,16 +6690,16 @@
         </is>
       </c>
       <c r="F134">
-        <v>665</v>
+        <v>733</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023605</t>
+          <t xml:space="preserve">200037719</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-09</t>
+          <t xml:space="preserve">2020-09-23</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6731,25 +6731,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716944</t>
+          <t xml:space="preserve">5710842</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F135">
-        <v>391</v>
+        <v>1063</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023681</t>
+          <t xml:space="preserve">200044849</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-10</t>
+          <t xml:space="preserve">2021-01-27</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">7070788</t>
+          <t xml:space="preserve">740183, 9680672</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -6790,16 +6790,16 @@
         </is>
       </c>
       <c r="F136">
-        <v>455</v>
+        <v>1742</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023991</t>
+          <t xml:space="preserve">200044868</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-16</t>
+          <t xml:space="preserve">2021-01-27</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716419</t>
+          <t xml:space="preserve">4461243</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -6840,16 +6840,16 @@
         </is>
       </c>
       <c r="F137">
-        <v>399</v>
+        <v>4089</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024698</t>
+          <t xml:space="preserve">200046007</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-28</t>
+          <t xml:space="preserve">2021-02-23</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6881,25 +6881,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1475000</t>
+          <t xml:space="preserve">4461539</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F138">
-        <v>316</v>
+        <v>941</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025346</t>
+          <t xml:space="preserve">200045998</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-11</t>
+          <t xml:space="preserve">2021-02-23</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6931,25 +6931,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1475000</t>
+          <t xml:space="preserve">4499244</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F139">
-        <v>347</v>
+        <v>2625</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025346</t>
+          <t xml:space="preserve">200046003</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-11</t>
+          <t xml:space="preserve">2021-02-23</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5709252</t>
+          <t xml:space="preserve">4504175</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -6990,16 +6990,16 @@
         </is>
       </c>
       <c r="F140">
-        <v>845</v>
+        <v>969</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025544</t>
+          <t xml:space="preserve">200046016</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-16</t>
+          <t xml:space="preserve">2021-02-23</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7031,25 +7031,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">4494935</t>
+          <t xml:space="preserve">5716411</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F141">
-        <v>2185</v>
+        <v>440</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026093</t>
+          <t xml:space="preserve">200046010</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-22</t>
+          <t xml:space="preserve">2021-02-23</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7081,25 +7081,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">4494935</t>
+          <t xml:space="preserve">5716411</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F142">
-        <v>659</v>
+        <v>7902</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026092</t>
+          <t xml:space="preserve">200046010</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-22</t>
+          <t xml:space="preserve">2021-02-23</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7131,25 +7131,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">7727184</t>
+          <t xml:space="preserve">9447893</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F143">
-        <v>733</v>
+        <v>8776</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">200037719</t>
+          <t xml:space="preserve">200046008</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-23</t>
+          <t xml:space="preserve">2021-02-23</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7181,25 +7181,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">740183, 9680672</t>
+          <t xml:space="preserve">9447893</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F144">
-        <v>1742</v>
+        <v>960</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">200044868</t>
+          <t xml:space="preserve">200046008</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-27</t>
+          <t xml:space="preserve">2021-02-23</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">4461243</t>
+          <t xml:space="preserve">9447934</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -7240,11 +7240,11 @@
         </is>
       </c>
       <c r="F145">
-        <v>4089</v>
+        <v>11334</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046007</t>
+          <t xml:space="preserve">200045997</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -7281,25 +7281,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">4461539</t>
+          <t xml:space="preserve">1510489</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F146">
-        <v>941</v>
+        <v>5275</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045998</t>
+          <t xml:space="preserve">200046106</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-23</t>
+          <t xml:space="preserve">2021-02-25</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">4499244</t>
+          <t xml:space="preserve">5717415</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -7340,16 +7340,16 @@
         </is>
       </c>
       <c r="F147">
-        <v>2625</v>
+        <v>3427</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046003</t>
+          <t xml:space="preserve">200046114</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-23</t>
+          <t xml:space="preserve">2021-02-25</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7381,25 +7381,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">4504175</t>
+          <t xml:space="preserve">5717415</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F148">
-        <v>969</v>
+        <v>580</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046016</t>
+          <t xml:space="preserve">200046114</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-23</t>
+          <t xml:space="preserve">2021-02-25</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7431,25 +7431,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716411</t>
+          <t xml:space="preserve">5717415</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F149">
-        <v>7902</v>
+        <v>275</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046014</t>
+          <t xml:space="preserve">200046132</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-23</t>
+          <t xml:space="preserve">2021-02-25</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7481,25 +7481,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">9447893</t>
+          <t xml:space="preserve">5717415</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F150">
-        <v>8776</v>
+        <v>563</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046008</t>
+          <t xml:space="preserve">200046132</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-23</t>
+          <t xml:space="preserve">2021-02-25</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7531,25 +7531,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">9447893</t>
+          <t xml:space="preserve">5714736</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F151">
-        <v>960</v>
+        <v>9137</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046008</t>
+          <t xml:space="preserve">200046211</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-23</t>
+          <t xml:space="preserve">2021-02-28</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">9447934</t>
+          <t xml:space="preserve">9426094</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -7590,16 +7590,16 @@
         </is>
       </c>
       <c r="F152">
-        <v>11334</v>
+        <v>2419</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045997</t>
+          <t xml:space="preserve">200051776</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-23</t>
+          <t xml:space="preserve">2021-08-08</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510489</t>
+          <t xml:space="preserve">7030832</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -7640,16 +7640,16 @@
         </is>
       </c>
       <c r="F153">
-        <v>5275</v>
+        <v>2552</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046106</t>
+          <t xml:space="preserve">200051932</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-25</t>
+          <t xml:space="preserve">2021-08-15</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7681,25 +7681,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5717415</t>
+          <t xml:space="preserve">7030832</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F154">
-        <v>3427</v>
+        <v>581</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046114</t>
+          <t xml:space="preserve">200051923</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-25</t>
+          <t xml:space="preserve">2021-08-15</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7731,25 +7731,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5717415</t>
+          <t xml:space="preserve">1805662</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F155">
-        <v>580</v>
+        <v>2161</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046114</t>
+          <t xml:space="preserve">200051977</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-25</t>
+          <t xml:space="preserve">2021-08-16</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7781,25 +7781,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5717415</t>
+          <t xml:space="preserve">4462277</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F156">
-        <v>275</v>
+        <v>416</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046132</t>
+          <t xml:space="preserve">200051956</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-25</t>
+          <t xml:space="preserve">2021-08-16</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7831,25 +7831,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5717415</t>
+          <t xml:space="preserve">4495667</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F157">
-        <v>563</v>
+        <v>1218</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046132</t>
+          <t xml:space="preserve">200051969</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-25</t>
+          <t xml:space="preserve">2021-08-16</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7881,25 +7881,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5714736</t>
+          <t xml:space="preserve">4498460</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F158">
-        <v>9137</v>
+        <v>1575</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046211</t>
+          <t xml:space="preserve">200051971</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-28</t>
+          <t xml:space="preserve">2021-08-16</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">9426094</t>
+          <t xml:space="preserve">5709677</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -7940,16 +7940,16 @@
         </is>
       </c>
       <c r="F159">
-        <v>2419</v>
+        <v>326</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051776</t>
+          <t xml:space="preserve">200051953</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-08</t>
+          <t xml:space="preserve">2021-08-16</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">7030832</t>
+          <t xml:space="preserve">5713349</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -7990,16 +7990,16 @@
         </is>
       </c>
       <c r="F160">
-        <v>2552</v>
+        <v>5873</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051932</t>
+          <t xml:space="preserve">200051968</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-15</t>
+          <t xml:space="preserve">2021-08-16</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8031,25 +8031,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">7030832</t>
+          <t xml:space="preserve">740181, 5000804</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F161">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051923</t>
+          <t xml:space="preserve">200051973</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-15</t>
+          <t xml:space="preserve">2021-08-16</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8081,20 +8081,20 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805662</t>
+          <t xml:space="preserve">740181, 5000804</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F162">
-        <v>2161</v>
+        <v>285</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051977</t>
+          <t xml:space="preserve">200051973</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">342475</t>
+          <t xml:space="preserve">8084366</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -8140,11 +8140,11 @@
         </is>
       </c>
       <c r="F163">
-        <v>1027</v>
+        <v>448</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051961</t>
+          <t xml:space="preserve">200051955</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">4462277</t>
+          <t xml:space="preserve">10007044</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -8190,16 +8190,16 @@
         </is>
       </c>
       <c r="F164">
-        <v>416</v>
+        <v>1568</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051956</t>
+          <t xml:space="preserve">200052024</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-16</t>
+          <t xml:space="preserve">2021-08-17</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8231,25 +8231,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">4495667</t>
+          <t xml:space="preserve">4489012</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F165">
-        <v>1218</v>
+        <v>610</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051969</t>
+          <t xml:space="preserve">200052038</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-16</t>
+          <t xml:space="preserve">2021-08-17</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">4498460</t>
+          <t xml:space="preserve">4503909</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -8290,16 +8290,16 @@
         </is>
       </c>
       <c r="F166">
-        <v>1575</v>
+        <v>1829</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051971</t>
+          <t xml:space="preserve">200052025</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-16</t>
+          <t xml:space="preserve">2021-08-17</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5709677</t>
+          <t xml:space="preserve">4513886</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -8340,16 +8340,16 @@
         </is>
       </c>
       <c r="F167">
-        <v>326</v>
+        <v>1916</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051953</t>
+          <t xml:space="preserve">200052027</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-16</t>
+          <t xml:space="preserve">2021-08-17</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8381,25 +8381,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5713349</t>
+          <t xml:space="preserve">5709778</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F168">
-        <v>5873</v>
+        <v>461</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051968</t>
+          <t xml:space="preserve">200052010</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-16</t>
+          <t xml:space="preserve">2021-08-17</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">8084366</t>
+          <t xml:space="preserve">5710371</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -8440,16 +8440,16 @@
         </is>
       </c>
       <c r="F169">
-        <v>448</v>
+        <v>2736</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051955</t>
+          <t xml:space="preserve">200052019</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-16</t>
+          <t xml:space="preserve">2021-08-17</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">10007044</t>
+          <t xml:space="preserve">8342487</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -8490,11 +8490,11 @@
         </is>
       </c>
       <c r="F170">
-        <v>1568</v>
+        <v>451</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052024</t>
+          <t xml:space="preserve">200052020</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -8531,20 +8531,20 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">4489012</t>
+          <t xml:space="preserve">9447609</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F171">
-        <v>610</v>
+        <v>830</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052038</t>
+          <t xml:space="preserve">200052016</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">4503909</t>
+          <t xml:space="preserve">4461539</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -8590,16 +8590,16 @@
         </is>
       </c>
       <c r="F172">
-        <v>1829</v>
+        <v>4997</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052025</t>
+          <t xml:space="preserve">200052070</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-17</t>
+          <t xml:space="preserve">2021-08-18</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">4513886</t>
+          <t xml:space="preserve">4493934</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -8640,16 +8640,16 @@
         </is>
       </c>
       <c r="F173">
-        <v>1916</v>
+        <v>735</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052027</t>
+          <t xml:space="preserve">200052080</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-17</t>
+          <t xml:space="preserve">2021-08-18</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5709355</t>
+          <t xml:space="preserve">4503798</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -8690,16 +8690,16 @@
         </is>
       </c>
       <c r="F174">
-        <v>1640</v>
+        <v>5757</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052004</t>
+          <t xml:space="preserve">200052072</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-17</t>
+          <t xml:space="preserve">2021-08-18</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8736,20 +8736,20 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F175">
-        <v>355</v>
+        <v>1640</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052018</t>
+          <t xml:space="preserve">200052075</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-17</t>
+          <t xml:space="preserve">2021-08-18</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8781,25 +8781,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">5709778</t>
+          <t xml:space="preserve">5709355</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F176">
-        <v>461</v>
+        <v>355</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052010</t>
+          <t xml:space="preserve">200052075</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-17</t>
+          <t xml:space="preserve">2021-08-18</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5710371</t>
+          <t xml:space="preserve">5709451</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -8840,16 +8840,16 @@
         </is>
       </c>
       <c r="F177">
-        <v>2736</v>
+        <v>2057</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052019</t>
+          <t xml:space="preserve">200052074</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-17</t>
+          <t xml:space="preserve">2021-08-18</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">8342487</t>
+          <t xml:space="preserve">5710367</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -8890,16 +8890,16 @@
         </is>
       </c>
       <c r="F178">
-        <v>451</v>
+        <v>2174</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052020</t>
+          <t xml:space="preserve">200052077</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-17</t>
+          <t xml:space="preserve">2021-08-18</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8931,25 +8931,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">9447609</t>
+          <t xml:space="preserve">5715540</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F179">
-        <v>830</v>
+        <v>671</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052016</t>
+          <t xml:space="preserve">200052066</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-17</t>
+          <t xml:space="preserve">2021-08-18</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8981,25 +8981,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">9447964</t>
+          <t xml:space="preserve">5716411</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F180">
-        <v>313</v>
+        <v>2120</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052008</t>
+          <t xml:space="preserve">200052065</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-17</t>
+          <t xml:space="preserve">2021-08-18</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">4461539</t>
+          <t xml:space="preserve">5719403</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -9040,11 +9040,11 @@
         </is>
       </c>
       <c r="F181">
-        <v>4997</v>
+        <v>1573</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052070</t>
+          <t xml:space="preserve">200052064</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -9081,20 +9081,20 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">4493934</t>
+          <t xml:space="preserve">5719403</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F182">
-        <v>735</v>
+        <v>1031</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052080</t>
+          <t xml:space="preserve">200052064</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">4503798</t>
+          <t xml:space="preserve">8491428</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -9140,11 +9140,11 @@
         </is>
       </c>
       <c r="F183">
-        <v>5757</v>
+        <v>385</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052072</t>
+          <t xml:space="preserve">200052068</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">5709451</t>
+          <t xml:space="preserve">9745128</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -9190,11 +9190,11 @@
         </is>
       </c>
       <c r="F184">
-        <v>2057</v>
+        <v>2497</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052074</t>
+          <t xml:space="preserve">200052076</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5710367</t>
+          <t xml:space="preserve">4502940</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -9240,16 +9240,16 @@
         </is>
       </c>
       <c r="F185">
-        <v>2174</v>
+        <v>1913</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052077</t>
+          <t xml:space="preserve">200052405</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-18</t>
+          <t xml:space="preserve">2021-08-29</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9281,25 +9281,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5715540</t>
+          <t xml:space="preserve">5710367</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F186">
-        <v>671</v>
+        <v>718</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052066</t>
+          <t xml:space="preserve">200052406</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-18</t>
+          <t xml:space="preserve">2021-08-29</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9331,25 +9331,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716411</t>
+          <t xml:space="preserve">10213815</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F187">
-        <v>2120</v>
+        <v>302</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052065</t>
+          <t xml:space="preserve">200052415</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-18</t>
+          <t xml:space="preserve">2021-08-30</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9381,25 +9381,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5719403</t>
+          <t xml:space="preserve">5709355</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F188">
-        <v>1573</v>
+        <v>920</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052064</t>
+          <t xml:space="preserve">200052412</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-18</t>
+          <t xml:space="preserve">2021-08-30</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9431,25 +9431,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">5719403</t>
+          <t xml:space="preserve">5709778</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F189">
-        <v>1031</v>
+        <v>266</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052064</t>
+          <t xml:space="preserve">200052413</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-18</t>
+          <t xml:space="preserve">2021-08-30</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">8491428</t>
+          <t xml:space="preserve">5714090</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -9490,16 +9490,16 @@
         </is>
       </c>
       <c r="F190">
-        <v>385</v>
+        <v>874</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052068</t>
+          <t xml:space="preserve">200052422</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-18</t>
+          <t xml:space="preserve">2021-08-30</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">9745128</t>
+          <t xml:space="preserve">8342484</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -9540,16 +9540,16 @@
         </is>
       </c>
       <c r="F191">
-        <v>2497</v>
+        <v>670</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052076</t>
+          <t xml:space="preserve">200052419</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-18</t>
+          <t xml:space="preserve">2021-08-30</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">4502940</t>
+          <t xml:space="preserve">9071236</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -9590,16 +9590,16 @@
         </is>
       </c>
       <c r="F192">
-        <v>1913</v>
+        <v>7053</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052405</t>
+          <t xml:space="preserve">200052564</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-29</t>
+          <t xml:space="preserve">2021-09-02</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -9631,25 +9631,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5710367</t>
+          <t xml:space="preserve">9447964</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F193">
-        <v>718</v>
+        <v>313</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052406</t>
+          <t xml:space="preserve">200053650</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-29</t>
+          <t xml:space="preserve">2021-10-07</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -9681,25 +9681,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">10213815</t>
+          <t xml:space="preserve">9447964</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F194">
-        <v>302</v>
+        <v>556</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052415</t>
+          <t xml:space="preserve">200053650</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-30</t>
+          <t xml:space="preserve">2021-10-07</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -9736,20 +9736,20 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F195">
-        <v>920</v>
+        <v>1028</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052412</t>
+          <t xml:space="preserve">200053776</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-30</t>
+          <t xml:space="preserve">2021-10-11</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5709778</t>
+          <t xml:space="preserve">5716802</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -9790,16 +9790,16 @@
         </is>
       </c>
       <c r="F196">
-        <v>266</v>
+        <v>4440</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052413</t>
+          <t xml:space="preserve">200053775</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-30</t>
+          <t xml:space="preserve">2021-10-11</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -9831,7 +9831,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5714090</t>
+          <t xml:space="preserve">9123977</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -9840,16 +9840,16 @@
         </is>
       </c>
       <c r="F197">
-        <v>874</v>
+        <v>465</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052422</t>
+          <t xml:space="preserve">200053764</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-30</t>
+          <t xml:space="preserve">2021-10-11</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">8342484</t>
+          <t xml:space="preserve">5000541</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -9890,16 +9890,16 @@
         </is>
       </c>
       <c r="F198">
-        <v>670</v>
+        <v>309</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052419</t>
+          <t xml:space="preserve">200053848</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-30</t>
+          <t xml:space="preserve">2021-10-13</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">9071236</t>
+          <t xml:space="preserve">4503816</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -9940,16 +9940,16 @@
         </is>
       </c>
       <c r="F199">
-        <v>7053</v>
+        <v>1086</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052564</t>
+          <t xml:space="preserve">200053970</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-09-02</t>
+          <t xml:space="preserve">2021-10-18</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -9981,25 +9981,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5709355</t>
+          <t xml:space="preserve">4488794</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F200">
-        <v>1028</v>
+        <v>1302</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053776</t>
+          <t xml:space="preserve">200054101</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-10-11</t>
+          <t xml:space="preserve">2021-10-24</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -10031,25 +10031,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716802</t>
+          <t xml:space="preserve">9992464</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F201">
-        <v>4440</v>
+        <v>4587</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053775</t>
+          <t xml:space="preserve">200054102</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-10-11</t>
+          <t xml:space="preserve">2021-10-24</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -10081,7 +10081,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123977</t>
+          <t xml:space="preserve">4514074</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -10090,16 +10090,16 @@
         </is>
       </c>
       <c r="F202">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053764</t>
+          <t xml:space="preserve">200054476</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-10-11</t>
+          <t xml:space="preserve">2021-11-01</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -10131,25 +10131,25 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000541</t>
+          <t xml:space="preserve">9447964</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F203">
-        <v>309</v>
+        <v>1470</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053848</t>
+          <t xml:space="preserve">200054618</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-10-13</t>
+          <t xml:space="preserve">2021-11-07</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -10181,25 +10181,25 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">4503816</t>
+          <t xml:space="preserve">5709355</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F204">
-        <v>1086</v>
+        <v>742</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053970</t>
+          <t xml:space="preserve">200054906</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-10-18</t>
+          <t xml:space="preserve">2021-11-16</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">4488794</t>
+          <t xml:space="preserve">4512513</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -10240,16 +10240,16 @@
         </is>
       </c>
       <c r="F205">
-        <v>1302</v>
+        <v>410</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054101</t>
+          <t xml:space="preserve">200055067</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-10-24</t>
+          <t xml:space="preserve">2021-11-21</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -10281,25 +10281,25 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">9992464</t>
+          <t xml:space="preserve">8624245</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F206">
-        <v>4587</v>
+        <v>5811</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054102</t>
+          <t xml:space="preserve">200055303</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-10-24</t>
+          <t xml:space="preserve">2021-12-01</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">4514074</t>
+          <t xml:space="preserve">9447925</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -10340,16 +10340,16 @@
         </is>
       </c>
       <c r="F207">
-        <v>480</v>
+        <v>2346</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054476</t>
+          <t xml:space="preserve">200055355</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-01</t>
+          <t xml:space="preserve">2021-12-01</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -10381,25 +10381,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">9447964</t>
+          <t xml:space="preserve">9447925</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F208">
-        <v>1470</v>
+        <v>554</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054618</t>
+          <t xml:space="preserve">200055355</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-07</t>
+          <t xml:space="preserve">2021-12-01</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -10431,25 +10431,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">5709355</t>
+          <t xml:space="preserve">9447925</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F209">
-        <v>742</v>
+        <v>498</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054906</t>
+          <t xml:space="preserve">200055355</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-16</t>
+          <t xml:space="preserve">2021-12-01</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">4512513</t>
+          <t xml:space="preserve">7831581</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -10490,16 +10490,16 @@
         </is>
       </c>
       <c r="F210">
-        <v>410</v>
+        <v>339</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055067</t>
+          <t xml:space="preserve">200058327</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-21</t>
+          <t xml:space="preserve">2022-03-22</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">8624245</t>
+          <t xml:space="preserve">9911653</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -10540,16 +10540,16 @@
         </is>
       </c>
       <c r="F211">
-        <v>5811</v>
+        <v>2632</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055303</t>
+          <t xml:space="preserve">200059626</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-01</t>
+          <t xml:space="preserve">2022-05-21</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -10581,25 +10581,25 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">9447925</t>
+          <t xml:space="preserve">4502934</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F212">
-        <v>2346</v>
+        <v>1879</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055355</t>
+          <t xml:space="preserve">310016737</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-01</t>
+          <t xml:space="preserve">2022-12-10</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -10631,25 +10631,25 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">9447925</t>
+          <t xml:space="preserve">10091953</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F213">
-        <v>554</v>
+        <v>332</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055355</t>
+          <t xml:space="preserve">310017010</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-01</t>
+          <t xml:space="preserve">2022-12-11</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -10681,25 +10681,25 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">9447925</t>
+          <t xml:space="preserve">10091953</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F214">
-        <v>498</v>
+        <v>804</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055355</t>
+          <t xml:space="preserve">310017010</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-01</t>
+          <t xml:space="preserve">2022-12-11</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -10731,25 +10731,25 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">7831581</t>
+          <t xml:space="preserve">5708896</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F215">
-        <v>339</v>
+        <v>3165</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">200058327</t>
+          <t xml:space="preserve">310035385</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-03-22</t>
+          <t xml:space="preserve">2023-04-16</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -10781,25 +10781,25 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">9911653</t>
+          <t xml:space="preserve">740239, 5710277</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F216">
-        <v>2632</v>
+        <v>541</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">200059626</t>
+          <t xml:space="preserve">311033996</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-05-21</t>
+          <t xml:space="preserve">2024-01-16</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -10831,25 +10831,25 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">4502934</t>
+          <t xml:space="preserve">740239, 5710277</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F217">
-        <v>1879</v>
+        <v>794</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">310016737</t>
+          <t xml:space="preserve">311033996</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-12-10</t>
+          <t xml:space="preserve">2024-01-16</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -10881,25 +10881,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">10091953</t>
+          <t xml:space="preserve">4504311</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F218">
-        <v>332</v>
+        <v>813</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">310017010</t>
+          <t xml:space="preserve">311069688</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-12-11</t>
+          <t xml:space="preserve">2024-08-22</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -10931,25 +10931,25 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">10091953</t>
+          <t xml:space="preserve">4489755</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F219">
-        <v>804</v>
+        <v>264</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">310017010</t>
+          <t xml:space="preserve">311145095</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-12-11</t>
+          <t xml:space="preserve">2025-11-13</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -10981,25 +10981,25 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">5708896</t>
+          <t xml:space="preserve">8491428</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F220">
-        <v>3165</v>
+        <v>1545</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">310035385</t>
+          <t xml:space="preserve">311190897</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-04-16</t>
+          <t xml:space="preserve">2026-07-20</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -11031,35 +11031,35 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">4489755</t>
+          <t xml:space="preserve">8289020</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F221">
-        <v>264</v>
+        <v>1540</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145095</t>
+          <t xml:space="preserve">311231161</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-13</t>
+          <t xml:space="preserve">2027-02-28</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -11081,35 +11081,35 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">8491428</t>
+          <t xml:space="preserve">100068272</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F222">
-        <v>1545</v>
+        <v>1424</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190897</t>
+          <t xml:space="preserve">311286529</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-20</t>
+          <t xml:space="preserve">2027-11-30</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -11131,25 +11131,25 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">8289020</t>
+          <t xml:space="preserve">740207, 100086993</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F223">
-        <v>1540</v>
+        <v>625</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231161</t>
+          <t xml:space="preserve">311289817</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-28</t>
+          <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">100068272</t>
+          <t xml:space="preserve">7728552</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -11190,16 +11190,16 @@
         </is>
       </c>
       <c r="F224">
-        <v>1424</v>
+        <v>533</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286529</t>
+          <t xml:space="preserve">311545449</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-30</t>
+          <t xml:space="preserve">2031-09-02</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -11231,25 +11231,25 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">740207, 100086993</t>
+          <t xml:space="preserve">1805766</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F225">
-        <v>625</v>
+        <v>2191</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289817</t>
+          <t xml:space="preserve">311548690</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-20</t>
+          <t xml:space="preserve">2031-09-16</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -11281,25 +11281,25 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">7728552</t>
+          <t xml:space="preserve">1805766</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F226">
-        <v>533</v>
+        <v>340</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311545449</t>
+          <t xml:space="preserve">311548678</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-02</t>
+          <t xml:space="preserve">2031-09-16</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805766</t>
+          <t xml:space="preserve">4488148</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -11340,11 +11340,11 @@
         </is>
       </c>
       <c r="F227">
-        <v>2191</v>
+        <v>1319</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548690</t>
+          <t xml:space="preserve">311548696</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -11381,20 +11381,20 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805766</t>
+          <t xml:space="preserve">4488148</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F228">
-        <v>340</v>
+        <v>1429</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548678</t>
+          <t xml:space="preserve">311548705</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -11431,25 +11431,25 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t xml:space="preserve">4488148</t>
+          <t xml:space="preserve">9447934</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F229">
-        <v>1319</v>
+        <v>3945</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548696</t>
+          <t xml:space="preserve">311558564</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-16</t>
+          <t xml:space="preserve">2031-10-29</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -11481,25 +11481,25 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t xml:space="preserve">4488148</t>
+          <t xml:space="preserve">5717678</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F230">
-        <v>1429</v>
+        <v>1635</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548705</t>
+          <t xml:space="preserve">311629747</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-16</t>
+          <t xml:space="preserve">2032-09-21</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -11531,25 +11531,25 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">9447934</t>
+          <t xml:space="preserve">5713127</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F231">
-        <v>3945</v>
+        <v>551</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558564</t>
+          <t xml:space="preserve">311727045</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-29</t>
+          <t xml:space="preserve">2033-09-28</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -11581,7 +11581,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">5717678</t>
+          <t xml:space="preserve">5719658</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -11590,16 +11590,16 @@
         </is>
       </c>
       <c r="F232">
-        <v>1635</v>
+        <v>1901</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311629747</t>
+          <t xml:space="preserve">311743759</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-21</t>
+          <t xml:space="preserve">2034-01-22</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -11631,25 +11631,25 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">5713127</t>
+          <t xml:space="preserve">9447934</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F233">
-        <v>551</v>
+        <v>977</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727045</t>
+          <t xml:space="preserve">311734366</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-28</t>
+          <t xml:space="preserve">2034-01-22</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t xml:space="preserve">5719658</t>
+          <t xml:space="preserve">5709649</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -11690,16 +11690,16 @@
         </is>
       </c>
       <c r="F234">
-        <v>1901</v>
+        <v>361</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743759</t>
+          <t xml:space="preserve">311804163</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-22</t>
+          <t xml:space="preserve">2034-12-23</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -11731,25 +11731,25 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">9447934</t>
+          <t xml:space="preserve">5719616</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F235">
-        <v>977</v>
+        <v>605</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311734366</t>
+          <t xml:space="preserve">311804162</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-22</t>
+          <t xml:space="preserve">2034-12-23</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">5709649</t>
+          <t xml:space="preserve">9447915</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -11790,11 +11790,11 @@
         </is>
       </c>
       <c r="F236">
-        <v>361</v>
+        <v>527</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311804163</t>
+          <t xml:space="preserve">311804164</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">5719616</t>
+          <t xml:space="preserve">8014311</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -11840,16 +11840,16 @@
         </is>
       </c>
       <c r="F237">
-        <v>605</v>
+        <v>560</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311804162</t>
+          <t xml:space="preserve">311812140</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-23</t>
+          <t xml:space="preserve">2035-02-17</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">9447915</t>
+          <t xml:space="preserve">5715275</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -11890,16 +11890,16 @@
         </is>
       </c>
       <c r="F238">
-        <v>527</v>
+        <v>609</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311804164</t>
+          <t xml:space="preserve">311812175</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-23</t>
+          <t xml:space="preserve">2035-02-18</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">8014311</t>
+          <t xml:space="preserve">5720630</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -11940,16 +11940,16 @@
         </is>
       </c>
       <c r="F239">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311812140</t>
+          <t xml:space="preserve">311812171</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-17</t>
+          <t xml:space="preserve">2035-02-18</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">5715275</t>
+          <t xml:space="preserve">8064298</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -11990,11 +11990,11 @@
         </is>
       </c>
       <c r="F240">
-        <v>609</v>
+        <v>559</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311812175</t>
+          <t xml:space="preserve">311812166</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">5720630</t>
+          <t xml:space="preserve">8561221</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -12040,11 +12040,11 @@
         </is>
       </c>
       <c r="F241">
-        <v>562</v>
+        <v>589</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311812171</t>
+          <t xml:space="preserve">311812173</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">8064298</t>
+          <t xml:space="preserve">5713169</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -12090,16 +12090,16 @@
         </is>
       </c>
       <c r="F242">
-        <v>559</v>
+        <v>526</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311812166</t>
+          <t xml:space="preserve">311813305</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-18</t>
+          <t xml:space="preserve">2035-02-21</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">8561221</t>
+          <t xml:space="preserve">5717689</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -12140,16 +12140,16 @@
         </is>
       </c>
       <c r="F243">
-        <v>589</v>
+        <v>488</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311812173</t>
+          <t xml:space="preserve">311813314</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-18</t>
+          <t xml:space="preserve">2035-02-21</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -12181,7 +12181,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">5713169</t>
+          <t xml:space="preserve">5717893</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -12190,11 +12190,11 @@
         </is>
       </c>
       <c r="F244">
-        <v>526</v>
+        <v>1203</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813305</t>
+          <t xml:space="preserve">311813308</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">5717689</t>
+          <t xml:space="preserve">5718883</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -12240,11 +12240,11 @@
         </is>
       </c>
       <c r="F245">
-        <v>488</v>
+        <v>577</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813314</t>
+          <t xml:space="preserve">311813312</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -12281,20 +12281,20 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">5717893</t>
+          <t xml:space="preserve">5718883</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F246">
-        <v>1203</v>
+        <v>431</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813308</t>
+          <t xml:space="preserve">311813312</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -12331,25 +12331,25 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">5718883</t>
+          <t xml:space="preserve">740626, 8875947</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F247">
-        <v>577</v>
+        <v>293</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813312</t>
+          <t xml:space="preserve">311847003</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-21</t>
+          <t xml:space="preserve">2035-08-01</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -12381,25 +12381,25 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">5718883</t>
+          <t xml:space="preserve">8875947</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F248">
-        <v>431</v>
+        <v>1968</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813312</t>
+          <t xml:space="preserve">311847003</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-21</t>
+          <t xml:space="preserve">2035-08-01</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">

--- a/public/exports/29189927.xlsx
+++ b/public/exports/29189927.xlsx
@@ -91,17 +91,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 37</t>
+          <t xml:space="preserve">Banevænget 9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">7830</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100024810</t>
+          <t xml:space="preserve">10016618</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -110,7 +110,7 @@
         </is>
       </c>
       <c r="H2">
-        <v>7835</v>
+        <v>252</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,7 +151,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemtoft 7</t>
+          <t xml:space="preserve">Bisgårdmark 14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -161,16 +161,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100065602</t>
+          <t xml:space="preserve">5716944</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H3">
-        <v>1815</v>
+        <v>689</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,26 +211,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banevænget 9</t>
+          <t xml:space="preserve">Bisgårdmark 16</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7830</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10016618</t>
+          <t xml:space="preserve">5716944</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H4">
-        <v>252</v>
+        <v>319</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harald Leths Vej 4</t>
+          <t xml:space="preserve">Bisgårdmark 16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -281,16 +281,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10213815</t>
+          <t xml:space="preserve">5716944</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H5">
-        <v>1003</v>
+        <v>319</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harald Leths Vej 4</t>
+          <t xml:space="preserve">Bisgårdmark 16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,16 +341,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">10213815</t>
+          <t xml:space="preserve">5716944</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H6">
-        <v>359</v>
+        <v>271</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,7 +391,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harald Leths Vej 4</t>
+          <t xml:space="preserve">Boldhusgade 1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -401,16 +401,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">10213815</t>
+          <t xml:space="preserve">5714270</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H7">
-        <v>578</v>
+        <v>406</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,26 +451,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harald Leths Vej 4</t>
+          <t xml:space="preserve">Brandsbjergvej 4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">7570</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10213815</t>
+          <t xml:space="preserve">740256, 7190859</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H8">
-        <v>336</v>
+        <v>1014</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,26 +511,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harald Leths Vej 4</t>
+          <t xml:space="preserve">Burvej 2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">7570</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">10213815</t>
+          <t xml:space="preserve">4495667</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H9">
-        <v>472</v>
+        <v>1089</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harald Leths Vej 4</t>
+          <t xml:space="preserve">Danmarksgade 7A</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,16 +581,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">10213815</t>
+          <t xml:space="preserve">9413823</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H10">
-        <v>934</v>
+        <v>640</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybovej 28</t>
+          <t xml:space="preserve">Den Røde Plads 16</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,16 +641,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1475000</t>
+          <t xml:space="preserve">342884, 342886</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H11">
-        <v>367</v>
+        <v>10411</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mozartsvej 5</t>
+          <t xml:space="preserve">Døesvej 56</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,16 +701,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510489</t>
+          <t xml:space="preserve">5710685</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H12">
-        <v>4525</v>
+        <v>3613</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mozartsvej 5</t>
+          <t xml:space="preserve">Elkjærvej 26A</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -761,16 +761,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510489</t>
+          <t xml:space="preserve">740586, 9777442</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H13">
-        <v>487</v>
+        <v>1942</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mozartsvej 5</t>
+          <t xml:space="preserve">Elkjærvej 26A</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -821,16 +821,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510489</t>
+          <t xml:space="preserve">740586, 9777442</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H14">
-        <v>820</v>
+        <v>541</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,26 +871,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 12</t>
+          <t xml:space="preserve">Elkjærvej 26A</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">7570</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805662</t>
+          <t xml:space="preserve">740586, 9777442</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H15">
-        <v>2559</v>
+        <v>1403</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danmarksgade 3</t>
+          <t xml:space="preserve">Elkjærvej 26A</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -941,16 +941,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">342475</t>
+          <t xml:space="preserve">740586, 9777442</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H16">
-        <v>1027</v>
+        <v>851</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,26 +991,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Den Røde Plads 16</t>
+          <t xml:space="preserve">Gl Landevej 22</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">7830</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">342884, 342886</t>
+          <t xml:space="preserve">740737, 4507216</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H17">
-        <v>10411</v>
+        <v>2032</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halgård Skolevej 3</t>
+          <t xml:space="preserve">Godthåbsvej 1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1061,16 +1061,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4461243</t>
+          <t xml:space="preserve">5709860</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H18">
-        <v>1870</v>
+        <v>452</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,26 +1111,26 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halgård Skolevej 3</t>
+          <t xml:space="preserve">Grønningen 23</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">7830</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4461243</t>
+          <t xml:space="preserve">9992464</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H19">
-        <v>1747</v>
+        <v>653</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevænget 1</t>
+          <t xml:space="preserve">Halgård Skolevej 3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1181,16 +1181,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4461367</t>
+          <t xml:space="preserve">4461243</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H20">
-        <v>420</v>
+        <v>1870</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevænget 4</t>
+          <t xml:space="preserve">Halgård Skolevej 3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4461539</t>
+          <t xml:space="preserve">4461243</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H21">
-        <v>286</v>
+        <v>1747</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,26 +1291,26 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viborgvej 203</t>
+          <t xml:space="preserve">Halvej 2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">7830</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4488794</t>
+          <t xml:space="preserve">4513886</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H22">
-        <v>1678</v>
+        <v>555</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,17 +1351,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejrup Kirkevej 11</t>
+          <t xml:space="preserve">Halvej 2A</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">7830</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4493849</t>
+          <t xml:space="preserve">740736, 4514043</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="H23">
-        <v>4767</v>
+        <v>487</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejrup Kirkevej 11</t>
+          <t xml:space="preserve">Harald Leths Vej 4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1421,16 +1421,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4493849</t>
+          <t xml:space="preserve">10213815</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H24">
-        <v>2749</v>
+        <v>1003</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejrup Kirkevej 11</t>
+          <t xml:space="preserve">Harald Leths Vej 4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1481,16 +1481,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">4493849</t>
+          <t xml:space="preserve">10213815</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H25">
-        <v>2067</v>
+        <v>359</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1531,17 +1531,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Burvej 2</t>
+          <t xml:space="preserve">Harald Leths Vej 4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">7570</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">4495667</t>
+          <t xml:space="preserve">10213815</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="H26">
-        <v>1089</v>
+        <v>578</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1591,26 +1591,26 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstegårdsvej 4</t>
+          <t xml:space="preserve">Harald Leths Vej 4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">7570</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4495687</t>
+          <t xml:space="preserve">10213815</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H27">
-        <v>790</v>
+        <v>336</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idomlundvej 23B</t>
+          <t xml:space="preserve">Harald Leths Vej 4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,16 +1661,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4498461</t>
+          <t xml:space="preserve">10213815</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H28">
-        <v>849</v>
+        <v>472</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1711,26 +1711,26 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindestien 16</t>
+          <t xml:space="preserve">Harald Leths Vej 4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">6990</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4503816</t>
+          <t xml:space="preserve">10213815</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H29">
-        <v>549</v>
+        <v>934</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindestien 34</t>
+          <t xml:space="preserve">Havnevej 2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1781,16 +1781,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4503816</t>
+          <t xml:space="preserve">740664, 4501285</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="H30">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1831,26 +1831,26 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindestien 44</t>
+          <t xml:space="preserve">Herningvej 74</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">6990</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4503816</t>
+          <t xml:space="preserve">9447925</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H31">
-        <v>2341</v>
+        <v>367</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1891,26 +1891,26 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 1</t>
+          <t xml:space="preserve">Hjaltesvej 1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">6990</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4504175</t>
+          <t xml:space="preserve">5719403</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H32">
-        <v>1763</v>
+        <v>1611</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1951,26 +1951,26 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 1</t>
+          <t xml:space="preserve">Hjerlhedevej 1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">6990</t>
+          <t xml:space="preserve">7830</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4504175</t>
+          <t xml:space="preserve">9123977</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H33">
-        <v>2601</v>
+        <v>338</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2011,26 +2011,26 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 1</t>
+          <t xml:space="preserve">Hjerlhedevej 1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">6990</t>
+          <t xml:space="preserve">7830</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">4504175</t>
+          <t xml:space="preserve">9123977</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H34">
-        <v>398</v>
+        <v>284</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nr Bjertvej 6</t>
+          <t xml:space="preserve">Hjerlhedevej 1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2081,16 +2081,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4511782</t>
+          <t xml:space="preserve">9123977</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H35">
-        <v>825</v>
+        <v>444</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvej 2</t>
+          <t xml:space="preserve">Hjerlhedevej 1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2141,16 +2141,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4513886</t>
+          <t xml:space="preserve">9123977</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H36">
-        <v>555</v>
+        <v>638</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2191,26 +2191,26 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skoletoften 3</t>
+          <t xml:space="preserve">Hvamvej 84</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">7830</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000571</t>
+          <t xml:space="preserve">740587, 7030832</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H37">
-        <v>1332</v>
+        <v>378</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2251,26 +2251,26 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skoletoften 3</t>
+          <t xml:space="preserve">Hvamvej 84</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">7830</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000571</t>
+          <t xml:space="preserve">740587, 7030832</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H38">
-        <v>419</v>
+        <v>391</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2311,26 +2311,26 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skoletoften 3</t>
+          <t xml:space="preserve">Hvamvej 84</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">7830</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000571</t>
+          <t xml:space="preserve">740587, 7030832</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H39">
-        <v>431</v>
+        <v>1953</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkestræde 13</t>
+          <t xml:space="preserve">Idomlundvej 23A</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2381,16 +2381,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5708896</t>
+          <t xml:space="preserve">740250, 4498461</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H40">
-        <v>4686</v>
+        <v>2606</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkestræde 11</t>
+          <t xml:space="preserve">Idomlundvej 23B</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2441,16 +2441,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5708896</t>
+          <t xml:space="preserve">4498461</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H41">
-        <v>10966</v>
+        <v>849</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Hallen 15</t>
+          <t xml:space="preserve">Idrætsvej 28</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,16 +2501,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5709728</t>
+          <t xml:space="preserve">8672254</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H42">
-        <v>1182</v>
+        <v>286</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 1</t>
+          <t xml:space="preserve">Idrætsvej 30</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5709860</t>
+          <t xml:space="preserve">8672254, 100331202</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="H43">
-        <v>452</v>
+        <v>1570</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Museumsvej 2B</t>
+          <t xml:space="preserve">Jeppe Schous Gade 12</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2621,16 +2621,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5710371</t>
+          <t xml:space="preserve">7900891</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H44">
-        <v>3090</v>
+        <v>3989</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døesvej 56</t>
+          <t xml:space="preserve">Kirkestræde 11</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2681,16 +2681,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5710685</t>
+          <t xml:space="preserve">5708896</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H45">
-        <v>3613</v>
+        <v>10966</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 88</t>
+          <t xml:space="preserve">Kirkestræde 13</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2741,16 +2741,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5712180</t>
+          <t xml:space="preserve">5708896</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H46">
-        <v>4028</v>
+        <v>4686</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 86</t>
+          <t xml:space="preserve">Kirkevænget 1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5712186</t>
+          <t xml:space="preserve">4461367</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="H47">
-        <v>600</v>
+        <v>420</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 90</t>
+          <t xml:space="preserve">Kirkevænget 4</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2861,16 +2861,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5712186</t>
+          <t xml:space="preserve">4461539</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H48">
-        <v>2395</v>
+        <v>286</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lystanlægget 3</t>
+          <t xml:space="preserve">Kirkevænget 8</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2921,16 +2921,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5713126</t>
+          <t xml:space="preserve">740268, 4461539</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H49">
-        <v>379</v>
+        <v>2916</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">V F Welschs Vej 11</t>
+          <t xml:space="preserve">Knud Rasmussens Vej 16</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2981,16 +2981,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5713665</t>
+          <t xml:space="preserve">5716802</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H50">
-        <v>462</v>
+        <v>260</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3031,17 +3031,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boldhusgade 1</t>
+          <t xml:space="preserve">Lillelundvej 10</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">7570</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5714270</t>
+          <t xml:space="preserve">8981629</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3050,7 +3050,7 @@
         </is>
       </c>
       <c r="H51">
-        <v>406</v>
+        <v>630</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3091,26 +3091,26 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebrogade 1</t>
+          <t xml:space="preserve">Lindestien 16</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">6990</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716420</t>
+          <t xml:space="preserve">4503816</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H52">
-        <v>610</v>
+        <v>549</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3151,26 +3151,26 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebrogade 1</t>
+          <t xml:space="preserve">Lindestien 34</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">6990</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716420</t>
+          <t xml:space="preserve">4503816</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H53">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3211,26 +3211,26 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knud Rasmussens Vej 16</t>
+          <t xml:space="preserve">Lindestien 44</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">6990</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716802</t>
+          <t xml:space="preserve">4503816</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H54">
-        <v>260</v>
+        <v>2341</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bisgårdmark 16</t>
+          <t xml:space="preserve">Lystanlægget 3</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3281,16 +3281,16 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716944</t>
+          <t xml:space="preserve">5713126</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H55">
-        <v>319</v>
+        <v>379</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bisgårdmark 16</t>
+          <t xml:space="preserve">Lystanlægget 4</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3341,16 +3341,16 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716944</t>
+          <t xml:space="preserve">9389974</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H56">
-        <v>319</v>
+        <v>497</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bisgårdmark 16</t>
+          <t xml:space="preserve">Lystanlægget 6</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3401,16 +3401,16 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716944</t>
+          <t xml:space="preserve">9389974</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="H57">
-        <v>271</v>
+        <v>320</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bisgårdmark 14</t>
+          <t xml:space="preserve">Lægårdvej 112</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3461,16 +3461,16 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716944</t>
+          <t xml:space="preserve">740244, 4493996</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H58">
-        <v>689</v>
+        <v>1500</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolf Krakes Vej 7A</t>
+          <t xml:space="preserve">Lægårdvej 112</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3521,16 +3521,16 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5719403</t>
+          <t xml:space="preserve">740244, 4493996</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H59">
-        <v>4675</v>
+        <v>1152</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjaltesvej 1</t>
+          <t xml:space="preserve">Mejrup Kirkevej 11</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3581,16 +3581,16 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5719403</t>
+          <t xml:space="preserve">4493849</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H60">
-        <v>1611</v>
+        <v>4767</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolf Krakes Vej 7A</t>
+          <t xml:space="preserve">Mejrup Kirkevej 11</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3641,16 +3641,16 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5719403</t>
+          <t xml:space="preserve">4493849</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H61">
-        <v>944</v>
+        <v>2749</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolf Krakes Vej 7A</t>
+          <t xml:space="preserve">Mejrup Kirkevej 11</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3701,16 +3701,16 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5719403</t>
+          <t xml:space="preserve">4493849</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H62">
-        <v>1156</v>
+        <v>2067</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolf Krakes Vej 7A</t>
+          <t xml:space="preserve">Mellemtoft 23</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3761,16 +3761,16 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5719403</t>
+          <t xml:space="preserve">8342484</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H63">
-        <v>370</v>
+        <v>670</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Struervej 30</t>
+          <t xml:space="preserve">Mellemtoft 25</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3821,16 +3821,16 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">7006806</t>
+          <t xml:space="preserve">8342484</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H64">
-        <v>3174</v>
+        <v>670</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Struervej 32</t>
+          <t xml:space="preserve">Mellemtoft 27</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3881,16 +3881,16 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">7006806</t>
+          <t xml:space="preserve">8342484</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H65">
-        <v>410</v>
+        <v>670</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Struervej 28E</t>
+          <t xml:space="preserve">Mellemtoft 29</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3941,16 +3941,16 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">7006806</t>
+          <t xml:space="preserve">8342484</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H66">
-        <v>8453</v>
+        <v>670</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Struervej 30G</t>
+          <t xml:space="preserve">Mellemtoft 31</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4001,16 +4001,16 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">7006806</t>
+          <t xml:space="preserve">8342484</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H67">
-        <v>6981</v>
+        <v>670</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nupark 55</t>
+          <t xml:space="preserve">Mellemtoft 7</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4061,16 +4061,16 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">740184, 9800976</t>
+          <t xml:space="preserve">100065602</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H68">
-        <v>1716</v>
+        <v>1815</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lægårdvej 112</t>
+          <t xml:space="preserve">Mozartsvej 5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4121,16 +4121,16 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">740244, 4493996</t>
+          <t xml:space="preserve">1510489</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H69">
-        <v>1500</v>
+        <v>4525</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lægårdvej 112</t>
+          <t xml:space="preserve">Mozartsvej 5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4181,16 +4181,16 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">740244, 4493996</t>
+          <t xml:space="preserve">1510489</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H70">
-        <v>1152</v>
+        <v>487</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søvej 6</t>
+          <t xml:space="preserve">Mozartsvej 5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4241,16 +4241,16 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">740247, 5712933</t>
+          <t xml:space="preserve">1510489</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H71">
-        <v>900</v>
+        <v>820</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søvej 8</t>
+          <t xml:space="preserve">Mozartsvej 7</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4301,16 +4301,16 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">740248, 5712934</t>
+          <t xml:space="preserve">740582, 1510489</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H72">
-        <v>366</v>
+        <v>300</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idomlundvej 23A</t>
+          <t xml:space="preserve">Museumsvej 2B</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4361,16 +4361,16 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">740250, 4498461</t>
+          <t xml:space="preserve">5710371</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H73">
-        <v>2606</v>
+        <v>3090</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storåvej 3</t>
+          <t xml:space="preserve">Niels Kjeldsens Vej 15</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4421,16 +4421,16 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">740254, 4493934</t>
+          <t xml:space="preserve">9447916</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H74">
-        <v>388</v>
+        <v>1312</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4471,17 +4471,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brandsbjergvej 4</t>
+          <t xml:space="preserve">Nr Bjertvej 6</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">7570</t>
+          <t xml:space="preserve">7830</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">740256, 7190859</t>
+          <t xml:space="preserve">4511782</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="H75">
-        <v>1014</v>
+        <v>825</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viborgvej 201</t>
+          <t xml:space="preserve">Nupark 55</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4541,16 +4541,16 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">740258, 4488794</t>
+          <t xml:space="preserve">740184, 9800976</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H76">
-        <v>1845</v>
+        <v>1716</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viborgvej 201</t>
+          <t xml:space="preserve">Nybovej 28</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4601,16 +4601,16 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">740258, 4488794</t>
+          <t xml:space="preserve">1475000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H77">
-        <v>1635</v>
+        <v>367</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sirvej 4B</t>
+          <t xml:space="preserve">Nørrebrogade 1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">740260, 4495015</t>
+          <t xml:space="preserve">5716420</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="H78">
-        <v>2002</v>
+        <v>610</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svinget 8D</t>
+          <t xml:space="preserve">Nørrebrogade 1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4721,16 +4721,16 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">740261, 5716124</t>
+          <t xml:space="preserve">5716420</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H79">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4766,22 +4766,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">661</t>
+          <t xml:space="preserve">671</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slåenvej 65</t>
+          <t xml:space="preserve">Oddesundvej 31</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">7600</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">740262, 9447609</t>
+          <t xml:space="preserve">8475859</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="H80">
-        <v>3010</v>
+        <v>275</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevænget 8</t>
+          <t xml:space="preserve">Parkvej 86</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4841,16 +4841,16 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">740268, 4461539</t>
+          <t xml:space="preserve">5712186</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H81">
-        <v>2916</v>
+        <v>600</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mozartsvej 7</t>
+          <t xml:space="preserve">Parkvej 88</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4901,16 +4901,16 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">740582, 1510489</t>
+          <t xml:space="preserve">5712180</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H82">
-        <v>300</v>
+        <v>4028</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elkjærvej 26A</t>
+          <t xml:space="preserve">Parkvej 90</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4961,16 +4961,16 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">740586, 9777442</t>
+          <t xml:space="preserve">5712186</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H83">
-        <v>1942</v>
+        <v>2395</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -5011,26 +5011,26 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elkjærvej 26A</t>
+          <t xml:space="preserve">Præstegårdsvej 4</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">7570</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">740586, 9777442</t>
+          <t xml:space="preserve">4495687</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H84">
-        <v>541</v>
+        <v>790</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elkjærvej 26A</t>
+          <t xml:space="preserve">Rolf Krakes Vej 7A</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5081,16 +5081,16 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">740586, 9777442</t>
+          <t xml:space="preserve">5719403</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H85">
-        <v>1403</v>
+        <v>4675</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elkjærvej 26A</t>
+          <t xml:space="preserve">Rolf Krakes Vej 7A</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5141,16 +5141,16 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">740586, 9777442</t>
+          <t xml:space="preserve">5719403</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H86">
-        <v>851</v>
+        <v>944</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvamvej 84</t>
+          <t xml:space="preserve">Rolf Krakes Vej 7A</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5201,16 +5201,16 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">740587, 7030832</t>
+          <t xml:space="preserve">5719403</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H87">
-        <v>378</v>
+        <v>1156</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvamvej 84</t>
+          <t xml:space="preserve">Rolf Krakes Vej 7A</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5261,16 +5261,16 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">740587, 7030832</t>
+          <t xml:space="preserve">5719403</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H88">
-        <v>391</v>
+        <v>370</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvamvej 84</t>
+          <t xml:space="preserve">Rolf Krakes Vej 9B</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5321,16 +5321,16 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">740587, 7030832</t>
+          <t xml:space="preserve">740592, 5719480</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H89">
-        <v>1953</v>
+        <v>1348</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolf Krakes Vej 9B</t>
+          <t xml:space="preserve">Sirvej 4B</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">740592, 5719480</t>
+          <t xml:space="preserve">740260, 4495015</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="H90">
-        <v>1348</v>
+        <v>2002</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -5431,26 +5431,26 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesthavnen 13</t>
+          <t xml:space="preserve">Skolegade 12</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">6990</t>
+          <t xml:space="preserve">7570</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">740662, 4501291</t>
+          <t xml:space="preserve">1805662</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H91">
-        <v>548</v>
+        <v>2559</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 2</t>
+          <t xml:space="preserve">Skolegade 25</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5501,16 +5501,16 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">740664, 4501285</t>
+          <t xml:space="preserve">8491428</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H92">
-        <v>317</v>
+        <v>729</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesthavnen 15</t>
+          <t xml:space="preserve">Skolegade 33</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5561,16 +5561,16 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">740669, 4501292</t>
+          <t xml:space="preserve">8491428</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">49</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H93">
-        <v>390</v>
+        <v>290</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvej 2A</t>
+          <t xml:space="preserve">Skoletoften 3</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">740736, 4514043</t>
+          <t xml:space="preserve">5000571</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="H94">
-        <v>487</v>
+        <v>1332</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Landevej 22</t>
+          <t xml:space="preserve">Skoletoften 3</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5681,16 +5681,16 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">740737, 4507216</t>
+          <t xml:space="preserve">5000571</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H95">
-        <v>2032</v>
+        <v>419</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5731,26 +5731,26 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeppe Schous Gade 12</t>
+          <t xml:space="preserve">Skoletoften 3</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">7830</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900891</t>
+          <t xml:space="preserve">5000571</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H96">
-        <v>3989</v>
+        <v>431</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervang 10</t>
+          <t xml:space="preserve">Slåenvej 65</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">8095136</t>
+          <t xml:space="preserve">740262, 9447609</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="H97">
-        <v>673</v>
+        <v>3010</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -5851,26 +5851,26 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderlundvej 2A</t>
+          <t xml:space="preserve">Sportsvej 1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">6990</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">8269227</t>
+          <t xml:space="preserve">4504175</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H98">
-        <v>316</v>
+        <v>1763</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5911,26 +5911,26 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemtoft 23</t>
+          <t xml:space="preserve">Sportsvej 1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">6990</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">8342484</t>
+          <t xml:space="preserve">4504175</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H99">
-        <v>670</v>
+        <v>2601</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5971,26 +5971,26 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemtoft 25</t>
+          <t xml:space="preserve">Sportsvej 1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">6990</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">8342484</t>
+          <t xml:space="preserve">4504175</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H100">
-        <v>670</v>
+        <v>398</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -6031,26 +6031,26 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemtoft 27</t>
+          <t xml:space="preserve">Stadionalle 2</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">7570</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">8342484</t>
+          <t xml:space="preserve">9745128</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H101">
-        <v>670</v>
+        <v>1025</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemtoft 29</t>
+          <t xml:space="preserve">Stationsvej 37</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6101,16 +6101,16 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">8342484</t>
+          <t xml:space="preserve">100024810</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H102">
-        <v>670</v>
+        <v>7835</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemtoft 31</t>
+          <t xml:space="preserve">Store Claus 7</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6161,16 +6161,16 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">8342484</t>
+          <t xml:space="preserve">9777442</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H103">
-        <v>670</v>
+        <v>1275</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -6206,31 +6206,31 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">671</t>
+          <t xml:space="preserve">661</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oddesundvej 31</t>
+          <t xml:space="preserve">Storåvej 3</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">7600</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">8475859</t>
+          <t xml:space="preserve">740254, 4493934</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H104">
-        <v>275</v>
+        <v>388</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -6271,26 +6271,26 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 25</t>
+          <t xml:space="preserve">Struervej 28E</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">6990</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">8491428</t>
+          <t xml:space="preserve">7006806</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H105">
-        <v>729</v>
+        <v>8453</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -6331,26 +6331,26 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 33</t>
+          <t xml:space="preserve">Struervej 30</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">6990</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">8491428</t>
+          <t xml:space="preserve">7006806</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H106">
-        <v>290</v>
+        <v>3174</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderlundvej 6</t>
+          <t xml:space="preserve">Struervej 30G</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6401,16 +6401,16 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">8630943</t>
+          <t xml:space="preserve">7006806</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H107">
-        <v>293</v>
+        <v>6981</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 28</t>
+          <t xml:space="preserve">Struervej 32</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6461,16 +6461,16 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">8672254</t>
+          <t xml:space="preserve">7006806</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H108">
-        <v>286</v>
+        <v>410</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 30</t>
+          <t xml:space="preserve">Svinget 8D</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">8672254, 100331202</t>
+          <t xml:space="preserve">740261, 5716124</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="H109">
-        <v>1570</v>
+        <v>254</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -6571,17 +6571,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lillelundvej 10</t>
+          <t xml:space="preserve">Sønder Alle 24</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">7570</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">8981629</t>
+          <t xml:space="preserve">9733938</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6590,7 +6590,7 @@
         </is>
       </c>
       <c r="H110">
-        <v>630</v>
+        <v>399</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -6631,26 +6631,26 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjerlhedevej 1</t>
+          <t xml:space="preserve">Sønderlundvej 2A</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">7830</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123977</t>
+          <t xml:space="preserve">8269227</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H111">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -6691,26 +6691,26 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjerlhedevej 1</t>
+          <t xml:space="preserve">Sønderlundvej 6</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">7830</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123977</t>
+          <t xml:space="preserve">8630943</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H112">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -6751,26 +6751,26 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjerlhedevej 1</t>
+          <t xml:space="preserve">Søvej 6</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">7830</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123977</t>
+          <t xml:space="preserve">740247, 5712933</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H113">
-        <v>444</v>
+        <v>900</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -6811,26 +6811,26 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjerlhedevej 1</t>
+          <t xml:space="preserve">Søvej 8</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">7830</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123977</t>
+          <t xml:space="preserve">740248, 5712934</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H114">
-        <v>638</v>
+        <v>366</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lystanlægget 4</t>
+          <t xml:space="preserve">V F Welschs Vej 11</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6881,16 +6881,16 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">9389974</t>
+          <t xml:space="preserve">5713665</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H115">
-        <v>497</v>
+        <v>462</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lystanlægget 6</t>
+          <t xml:space="preserve">Ved Hallen 15</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6941,16 +6941,16 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">9389974</t>
+          <t xml:space="preserve">5709728</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H116">
-        <v>320</v>
+        <v>1182</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -6991,26 +6991,26 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danmarksgade 7A</t>
+          <t xml:space="preserve">Vesthavnen 13</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">6990</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">9413823</t>
+          <t xml:space="preserve">740662, 4501291</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="H117">
-        <v>640</v>
+        <v>548</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -7051,26 +7051,26 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Kjeldsens Vej 15</t>
+          <t xml:space="preserve">Vesthavnen 15</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">6990</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">9447916</t>
+          <t xml:space="preserve">740669, 4501292</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">49</t>
         </is>
       </c>
       <c r="H118">
-        <v>1312</v>
+        <v>390</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herningvej 74</t>
+          <t xml:space="preserve">Viborgvej 201</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7121,16 +7121,16 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">9447925</t>
+          <t xml:space="preserve">740258, 4488794</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H119">
-        <v>367</v>
+        <v>1845</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønder Alle 24</t>
+          <t xml:space="preserve">Viborgvej 201</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7181,16 +7181,16 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9733938</t>
+          <t xml:space="preserve">740258, 4488794</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H120">
-        <v>399</v>
+        <v>1635</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -7231,26 +7231,26 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 2</t>
+          <t xml:space="preserve">Viborgvej 203</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">7570</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9745128</t>
+          <t xml:space="preserve">4488794</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H121">
-        <v>1025</v>
+        <v>1678</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store Claus 7</t>
+          <t xml:space="preserve">Østervang 10</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7301,16 +7301,16 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">9777442</t>
+          <t xml:space="preserve">8095136</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H122">
-        <v>1275</v>
+        <v>673</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 23</t>
+          <t xml:space="preserve">Vindelevgård 111</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7361,30 +7361,30 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9992464</t>
+          <t xml:space="preserve">4512452</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H123">
-        <v>653</v>
+        <v>285</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200013352</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-05-06</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -7411,17 +7411,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindelevgård 111</t>
+          <t xml:space="preserve">Holmegade 40</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">7830</t>
+          <t xml:space="preserve">6990</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">4512452</t>
+          <t xml:space="preserve">4503820</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -7430,16 +7430,16 @@
         </is>
       </c>
       <c r="H124">
-        <v>285</v>
+        <v>665</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">200013352</t>
+          <t xml:space="preserve">200023605</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-06</t>
+          <t xml:space="preserve">2019-11-09</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7471,17 +7471,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmegade 40</t>
+          <t xml:space="preserve">Bisgårdmark 16</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">6990</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">4503820</t>
+          <t xml:space="preserve">5716944</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7490,16 +7490,16 @@
         </is>
       </c>
       <c r="H125">
-        <v>665</v>
+        <v>391</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023605</t>
+          <t xml:space="preserve">200023681</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-09</t>
+          <t xml:space="preserve">2019-11-10</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7531,17 +7531,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bisgårdmark 16</t>
+          <t xml:space="preserve">Sportsvej 1</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">7830</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716944</t>
+          <t xml:space="preserve">7070788</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7550,16 +7550,16 @@
         </is>
       </c>
       <c r="H126">
-        <v>391</v>
+        <v>455</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023681</t>
+          <t xml:space="preserve">200023991</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-10</t>
+          <t xml:space="preserve">2019-11-16</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7591,17 +7591,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 1</t>
+          <t xml:space="preserve">Døesvej 3</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">7830</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">7070788</t>
+          <t xml:space="preserve">5716419</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -7610,16 +7610,16 @@
         </is>
       </c>
       <c r="H127">
-        <v>455</v>
+        <v>399</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023991</t>
+          <t xml:space="preserve">200024698</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-16</t>
+          <t xml:space="preserve">2019-11-28</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døesvej 3</t>
+          <t xml:space="preserve">Nybovej 28</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716419</t>
+          <t xml:space="preserve">1475000</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -7670,16 +7670,16 @@
         </is>
       </c>
       <c r="H128">
-        <v>399</v>
+        <v>316</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024698</t>
+          <t xml:space="preserve">200025346</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-28</t>
+          <t xml:space="preserve">2019-12-11</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7726,11 +7726,11 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H129">
-        <v>316</v>
+        <v>347</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybovej 28</t>
+          <t xml:space="preserve">Skivevej 7</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7781,25 +7781,25 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1475000</t>
+          <t xml:space="preserve">5709252</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H130">
-        <v>347</v>
+        <v>845</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025346</t>
+          <t xml:space="preserve">200025544</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-11</t>
+          <t xml:space="preserve">2019-12-16</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skivevej 7</t>
+          <t xml:space="preserve">Sirvej 3</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">5709252</t>
+          <t xml:space="preserve">4494935</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -7850,16 +7850,16 @@
         </is>
       </c>
       <c r="H131">
-        <v>845</v>
+        <v>2185</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025544</t>
+          <t xml:space="preserve">200026093</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-16</t>
+          <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sirvej 3</t>
+          <t xml:space="preserve">Sirvej 3A</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7906,15 +7906,15 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H132">
-        <v>2185</v>
+        <v>659</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026093</t>
+          <t xml:space="preserve">200026092</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sirvej 3A</t>
+          <t xml:space="preserve">Thorsvej 63</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7961,25 +7961,25 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">4494935</t>
+          <t xml:space="preserve">7727184</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H133">
-        <v>659</v>
+        <v>733</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026092</t>
+          <t xml:space="preserve">200037719</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-22</t>
+          <t xml:space="preserve">2020-09-23</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorsvej 63</t>
+          <t xml:space="preserve">Nupark 53</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">7727184</t>
+          <t xml:space="preserve">740183, 9680672</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -8030,16 +8030,16 @@
         </is>
       </c>
       <c r="H134">
-        <v>733</v>
+        <v>1742</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">200037719</t>
+          <t xml:space="preserve">200044868</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-23</t>
+          <t xml:space="preserve">2021-01-27</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nupark 53</t>
+          <t xml:space="preserve">Døesvej 54E</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8141,25 +8141,25 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">740183, 9680672</t>
+          <t xml:space="preserve">9447893</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H136">
-        <v>1742</v>
+        <v>960</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">200044868</t>
+          <t xml:space="preserve">200046008</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-27</t>
+          <t xml:space="preserve">2021-02-23</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halgård Skolevej 3</t>
+          <t xml:space="preserve">Døesvej 54F</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8201,20 +8201,20 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">4461243</t>
+          <t xml:space="preserve">9447893</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H137">
-        <v>4089</v>
+        <v>8776</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046007</t>
+          <t xml:space="preserve">200046008</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevænget 2</t>
+          <t xml:space="preserve">Halgård Skolevej 3</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8261,20 +8261,20 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">4461539</t>
+          <t xml:space="preserve">4461243</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H138">
-        <v>941</v>
+        <v>4089</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045998</t>
+          <t xml:space="preserve">200046007</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 7</t>
+          <t xml:space="preserve">Kirkevænget 2</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8321,20 +8321,20 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">4499244</t>
+          <t xml:space="preserve">4461539</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H139">
-        <v>2625</v>
+        <v>941</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046003</t>
+          <t xml:space="preserve">200045998</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8371,17 +8371,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 1</t>
+          <t xml:space="preserve">Nørre Boulevard 57</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">6990</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">4504175</t>
+          <t xml:space="preserve">9447934</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -8390,11 +8390,11 @@
         </is>
       </c>
       <c r="H140">
-        <v>969</v>
+        <v>11334</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046016</t>
+          <t xml:space="preserve">200045997</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046010</t>
+          <t xml:space="preserve">200046014</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døesvej 54F</t>
+          <t xml:space="preserve">Skolevej 7</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8561,20 +8561,20 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">9447893</t>
+          <t xml:space="preserve">4499244</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H143">
-        <v>8776</v>
+        <v>2625</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046008</t>
+          <t xml:space="preserve">200046003</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -8611,30 +8611,30 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døesvej 54E</t>
+          <t xml:space="preserve">Sportsvej 1</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">6990</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9447893</t>
+          <t xml:space="preserve">4504175</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H144">
-        <v>960</v>
+        <v>969</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046008</t>
+          <t xml:space="preserve">200046016</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Boulevard 57</t>
+          <t xml:space="preserve">Beethovensvej 24</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9447934</t>
+          <t xml:space="preserve">5717415</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -8690,16 +8690,16 @@
         </is>
       </c>
       <c r="H145">
-        <v>11334</v>
+        <v>3427</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045997</t>
+          <t xml:space="preserve">200046114</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-23</t>
+          <t xml:space="preserve">2021-02-25</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mozartsvej 5</t>
+          <t xml:space="preserve">Beethovensvej 24</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8741,20 +8741,20 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510489</t>
+          <t xml:space="preserve">5717415</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H146">
-        <v>5275</v>
+        <v>580</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046106</t>
+          <t xml:space="preserve">200046114</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8806,15 +8806,15 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H147">
-        <v>3427</v>
+        <v>563</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046114</t>
+          <t xml:space="preserve">200046132</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beethovensvej 24</t>
+          <t xml:space="preserve">Beethovensvej 26</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8866,15 +8866,15 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H148">
-        <v>580</v>
+        <v>275</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046114</t>
+          <t xml:space="preserve">200046132</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beethovensvej 26</t>
+          <t xml:space="preserve">Mozartsvej 5</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8921,20 +8921,20 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5717415</t>
+          <t xml:space="preserve">1510489</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H149">
-        <v>275</v>
+        <v>5275</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046132</t>
+          <t xml:space="preserve">200046106</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beethovensvej 24</t>
+          <t xml:space="preserve">Sønder Alle 25</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8981,25 +8981,25 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5717415</t>
+          <t xml:space="preserve">5714736</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H150">
-        <v>563</v>
+        <v>9137</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046132</t>
+          <t xml:space="preserve">200046211</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-25</t>
+          <t xml:space="preserve">2021-02-28</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9031,35 +9031,35 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønder Alle 25</t>
+          <t xml:space="preserve">Krohaven 1</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">7570</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5714736</t>
+          <t xml:space="preserve">9426094</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H151">
-        <v>9137</v>
+        <v>2419</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046211</t>
+          <t xml:space="preserve">200051776</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-28</t>
+          <t xml:space="preserve">2021-08-08</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9091,17 +9091,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krohaven 1</t>
+          <t xml:space="preserve">Bukdalvej 1</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">7570</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">9426094</t>
+          <t xml:space="preserve">7030832</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -9110,16 +9110,16 @@
         </is>
       </c>
       <c r="H152">
-        <v>2419</v>
+        <v>2552</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051776</t>
+          <t xml:space="preserve">200051932</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-08</t>
+          <t xml:space="preserve">2021-08-15</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bukdalvej 1</t>
+          <t xml:space="preserve">Bukdalvej 3</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9166,15 +9166,15 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H153">
-        <v>2552</v>
+        <v>581</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051932</t>
+          <t xml:space="preserve">200051923</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bukdalvej 3</t>
+          <t xml:space="preserve">Birkehøj 80</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9221,25 +9221,25 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">7030832</t>
+          <t xml:space="preserve">5713349</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H154">
-        <v>581</v>
+        <v>5873</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051923</t>
+          <t xml:space="preserve">200051968</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-15</t>
+          <t xml:space="preserve">2021-08-16</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9271,17 +9271,17 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 12</t>
+          <t xml:space="preserve">Birkevej 3A</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">7570</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805662</t>
+          <t xml:space="preserve">4462277</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -9290,11 +9290,11 @@
         </is>
       </c>
       <c r="H155">
-        <v>2161</v>
+        <v>416</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051977</t>
+          <t xml:space="preserve">200051956</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -9331,17 +9331,17 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevej 3A</t>
+          <t xml:space="preserve">Bjertparken 4</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">7830</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">4462277</t>
+          <t xml:space="preserve">8084366</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -9350,11 +9350,11 @@
         </is>
       </c>
       <c r="H156">
-        <v>416</v>
+        <v>448</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051956</t>
+          <t xml:space="preserve">200051955</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idomlundvej 27</t>
+          <t xml:space="preserve">Danmarksgade 3</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">4498460</t>
+          <t xml:space="preserve">342475</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -9470,11 +9470,11 @@
         </is>
       </c>
       <c r="H158">
-        <v>1575</v>
+        <v>1027</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051971</t>
+          <t xml:space="preserve">200051961</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 37</t>
+          <t xml:space="preserve">Idomlundvej 27</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5709677</t>
+          <t xml:space="preserve">4498460</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -9530,11 +9530,11 @@
         </is>
       </c>
       <c r="H159">
-        <v>326</v>
+        <v>1575</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051953</t>
+          <t xml:space="preserve">200051971</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9571,17 +9571,17 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkehøj 80</t>
+          <t xml:space="preserve">Skolegade 12</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">7570</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5713349</t>
+          <t xml:space="preserve">1805662</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -9590,11 +9590,11 @@
         </is>
       </c>
       <c r="H160">
-        <v>5873</v>
+        <v>2161</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051968</t>
+          <t xml:space="preserve">200051977</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -9751,17 +9751,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjertparken 4</t>
+          <t xml:space="preserve">Vestergade 37</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">7830</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">8084366</t>
+          <t xml:space="preserve">5709677</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -9770,11 +9770,11 @@
         </is>
       </c>
       <c r="H163">
-        <v>448</v>
+        <v>326</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051955</t>
+          <t xml:space="preserve">200051953</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -9811,30 +9811,30 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rydevej 10</t>
+          <t xml:space="preserve">Brogårdsvej 4</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">7830</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">10007044</t>
+          <t xml:space="preserve">5709778</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H164">
-        <v>1568</v>
+        <v>461</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052024</t>
+          <t xml:space="preserve">200052010</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -9931,17 +9931,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvej 5</t>
+          <t xml:space="preserve">Grønningen 1</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">6990</t>
+          <t xml:space="preserve">7830</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">4503909</t>
+          <t xml:space="preserve">4513886</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -9950,11 +9950,11 @@
         </is>
       </c>
       <c r="H166">
-        <v>1829</v>
+        <v>1916</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052025</t>
+          <t xml:space="preserve">200052027</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9991,17 +9991,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 1</t>
+          <t xml:space="preserve">Mellemtoft 17</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">7830</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">4513886</t>
+          <t xml:space="preserve">8342487</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -10010,11 +10010,11 @@
         </is>
       </c>
       <c r="H167">
-        <v>1916</v>
+        <v>451</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052027</t>
+          <t xml:space="preserve">200052020</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brogårdsvej 4</t>
+          <t xml:space="preserve">Museumsvej 2A</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10061,20 +10061,20 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5709778</t>
+          <t xml:space="preserve">5710371</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H168">
-        <v>461</v>
+        <v>2736</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052010</t>
+          <t xml:space="preserve">200052019</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -10111,17 +10111,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Museumsvej 2A</t>
+          <t xml:space="preserve">Rydevej 10</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">7830</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5710371</t>
+          <t xml:space="preserve">10007044</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -10130,11 +10130,11 @@
         </is>
       </c>
       <c r="H169">
-        <v>2736</v>
+        <v>1568</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052019</t>
+          <t xml:space="preserve">200052024</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemtoft 17</t>
+          <t xml:space="preserve">Slåenvej 63</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10181,20 +10181,20 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">8342487</t>
+          <t xml:space="preserve">9447609</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H170">
-        <v>451</v>
+        <v>830</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052020</t>
+          <t xml:space="preserve">200052016</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -10231,30 +10231,30 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slåenvej 63</t>
+          <t xml:space="preserve">Tingvej 5</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">6990</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">9447609</t>
+          <t xml:space="preserve">4503909</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H171">
-        <v>830</v>
+        <v>1829</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052016</t>
+          <t xml:space="preserve">200052025</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 1</t>
+          <t xml:space="preserve">Danmarksgade 13A</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">4461539</t>
+          <t xml:space="preserve">5709355</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -10310,11 +10310,11 @@
         </is>
       </c>
       <c r="H172">
-        <v>4997</v>
+        <v>1640</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052070</t>
+          <t xml:space="preserve">200052075</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storåvej 1</t>
+          <t xml:space="preserve">Danmarksgade 24</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">4493934</t>
+          <t xml:space="preserve">5709451</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -10370,11 +10370,11 @@
         </is>
       </c>
       <c r="H173">
-        <v>735</v>
+        <v>2057</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052080</t>
+          <t xml:space="preserve">200052074</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danmarksgade 13A</t>
+          <t xml:space="preserve">Nygade 22</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10486,11 +10486,11 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H175">
-        <v>1640</v>
+        <v>355</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 22</t>
+          <t xml:space="preserve">Odinsvej 2</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10541,20 +10541,20 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">5709355</t>
+          <t xml:space="preserve">5716411</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H176">
-        <v>355</v>
+        <v>2120</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052075</t>
+          <t xml:space="preserve">200052065</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danmarksgade 24</t>
+          <t xml:space="preserve">Rolf Krakes Vej 11</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5709451</t>
+          <t xml:space="preserve">5719403</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -10610,11 +10610,11 @@
         </is>
       </c>
       <c r="H177">
-        <v>2057</v>
+        <v>1573</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052074</t>
+          <t xml:space="preserve">200052064</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterbo 4</t>
+          <t xml:space="preserve">Rolf Krakes Vej 11</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10661,20 +10661,20 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5710367</t>
+          <t xml:space="preserve">5719403</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H178">
-        <v>2174</v>
+        <v>1031</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052077</t>
+          <t xml:space="preserve">200052064</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10711,17 +10711,17 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønder Alle 33A</t>
+          <t xml:space="preserve">Skolegade 25</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">6990</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5715540</t>
+          <t xml:space="preserve">8491428</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -10730,11 +10730,11 @@
         </is>
       </c>
       <c r="H179">
-        <v>671</v>
+        <v>385</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052066</t>
+          <t xml:space="preserve">200052068</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odinsvej 2</t>
+          <t xml:space="preserve">Skolevænget 1</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10781,20 +10781,20 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716411</t>
+          <t xml:space="preserve">4461539</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H180">
-        <v>2120</v>
+        <v>4997</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052065</t>
+          <t xml:space="preserve">200052070</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -10831,17 +10831,17 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolf Krakes Vej 11</t>
+          <t xml:space="preserve">Stadionalle 2</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">7570</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">5719403</t>
+          <t xml:space="preserve">9745128</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -10850,11 +10850,11 @@
         </is>
       </c>
       <c r="H181">
-        <v>1573</v>
+        <v>2497</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052064</t>
+          <t xml:space="preserve">200052076</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolf Krakes Vej 11</t>
+          <t xml:space="preserve">Storåvej 1</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10901,20 +10901,20 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5719403</t>
+          <t xml:space="preserve">4493934</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H182">
-        <v>1031</v>
+        <v>735</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052064</t>
+          <t xml:space="preserve">200052080</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -10951,17 +10951,17 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 25</t>
+          <t xml:space="preserve">Sønder Alle 33A</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">6990</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">8491428</t>
+          <t xml:space="preserve">5715540</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -10970,11 +10970,11 @@
         </is>
       </c>
       <c r="H183">
-        <v>385</v>
+        <v>671</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052068</t>
+          <t xml:space="preserve">200052066</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -11011,17 +11011,17 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 2</t>
+          <t xml:space="preserve">Vesterbo 4</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">7570</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">9745128</t>
+          <t xml:space="preserve">5710367</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -11030,11 +11030,11 @@
         </is>
       </c>
       <c r="H184">
-        <v>2497</v>
+        <v>2174</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052076</t>
+          <t xml:space="preserve">200052077</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harald Leths Vej 4</t>
+          <t xml:space="preserve">Brogårdsvej 2</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">10213815</t>
+          <t xml:space="preserve">5709778</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -11210,11 +11210,11 @@
         </is>
       </c>
       <c r="H187">
-        <v>302</v>
+        <v>266</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052415</t>
+          <t xml:space="preserve">200052413</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brogårdsvej 2</t>
+          <t xml:space="preserve">Harald Leths Vej 4</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">5709778</t>
+          <t xml:space="preserve">10213815</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -11330,11 +11330,11 @@
         </is>
       </c>
       <c r="H189">
-        <v>266</v>
+        <v>302</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052413</t>
+          <t xml:space="preserve">200052415</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 10</t>
+          <t xml:space="preserve">Mellemtoft 21</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5714090</t>
+          <t xml:space="preserve">8342484</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -11390,11 +11390,11 @@
         </is>
       </c>
       <c r="H190">
-        <v>874</v>
+        <v>670</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052422</t>
+          <t xml:space="preserve">200052419</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemtoft 21</t>
+          <t xml:space="preserve">Sportsvej 10</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">8342484</t>
+          <t xml:space="preserve">5714090</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -11450,11 +11450,11 @@
         </is>
       </c>
       <c r="H191">
-        <v>670</v>
+        <v>874</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052419</t>
+          <t xml:space="preserve">200052422</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -11731,17 +11731,17 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knud Rasmussens Vej 16</t>
+          <t xml:space="preserve">Hjerlhedevej 1</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">7830</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716802</t>
+          <t xml:space="preserve">9123977</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -11750,11 +11750,11 @@
         </is>
       </c>
       <c r="H196">
-        <v>4440</v>
+        <v>465</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053775</t>
+          <t xml:space="preserve">200053764</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -11791,17 +11791,17 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjerlhedevej 1</t>
+          <t xml:space="preserve">Knud Rasmussens Vej 16</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">7830</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123977</t>
+          <t xml:space="preserve">5716802</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -11810,11 +11810,11 @@
         </is>
       </c>
       <c r="H197">
-        <v>465</v>
+        <v>4440</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053764</t>
+          <t xml:space="preserve">200053775</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -11971,30 +11971,30 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viborgvej 203</t>
+          <t xml:space="preserve">Grønningen 19</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">7830</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">4488794</t>
+          <t xml:space="preserve">9992464</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H200">
-        <v>1302</v>
+        <v>4587</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054101</t>
+          <t xml:space="preserve">200054102</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -12031,30 +12031,30 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 19</t>
+          <t xml:space="preserve">Viborgvej 203</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">7830</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">9992464</t>
+          <t xml:space="preserve">4488794</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H201">
-        <v>4587</v>
+        <v>1302</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054102</t>
+          <t xml:space="preserve">200054101</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -12331,30 +12331,30 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sevelvej 27</t>
+          <t xml:space="preserve">Herningvej 74A</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">7830</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">8624245</t>
+          <t xml:space="preserve">9447925</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H206">
-        <v>5811</v>
+        <v>554</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055303</t>
+          <t xml:space="preserve">200055355</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herningvej 74A</t>
+          <t xml:space="preserve">Herningvej 74P</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -12466,11 +12466,11 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H208">
-        <v>554</v>
+        <v>498</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -12511,30 +12511,30 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herningvej 74P</t>
+          <t xml:space="preserve">Sevelvej 27</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">7830</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">9447925</t>
+          <t xml:space="preserve">8624245</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H209">
-        <v>498</v>
+        <v>5811</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055355</t>
+          <t xml:space="preserve">200055303</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -13471,17 +13471,17 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stabyvej 36</t>
+          <t xml:space="preserve">Grønnevang 12</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t xml:space="preserve">6990</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805766</t>
+          <t xml:space="preserve">4488148</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -13490,11 +13490,11 @@
         </is>
       </c>
       <c r="H225">
-        <v>2191</v>
+        <v>1319</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548690</t>
+          <t xml:space="preserve">311548696</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -13531,30 +13531,30 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stabyvej 34</t>
+          <t xml:space="preserve">Grønnevang 12A</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t xml:space="preserve">6990</t>
+          <t xml:space="preserve">7500</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805766</t>
+          <t xml:space="preserve">4488148</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H226">
-        <v>340</v>
+        <v>1429</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548678</t>
+          <t xml:space="preserve">311548705</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -13591,30 +13591,30 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevang 12</t>
+          <t xml:space="preserve">Stabyvej 34</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">6990</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">4488148</t>
+          <t xml:space="preserve">1805766</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H227">
-        <v>1319</v>
+        <v>340</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548696</t>
+          <t xml:space="preserve">311548678</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -13651,30 +13651,30 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevang 12A</t>
+          <t xml:space="preserve">Stabyvej 36</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t xml:space="preserve">7500</t>
+          <t xml:space="preserve">6990</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">4488148</t>
+          <t xml:space="preserve">1805766</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H228">
-        <v>1429</v>
+        <v>2191</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548705</t>
+          <t xml:space="preserve">311548690</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Platanvej 15</t>
+          <t xml:space="preserve">Helgolandsgade 53</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -14021,7 +14021,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">5709649</t>
+          <t xml:space="preserve">9447915</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -14030,11 +14030,11 @@
         </is>
       </c>
       <c r="H234">
-        <v>361</v>
+        <v>527</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311804163</t>
+          <t xml:space="preserve">311804164</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helgolandsgade 53</t>
+          <t xml:space="preserve">Platanvej 15</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">9447915</t>
+          <t xml:space="preserve">5709649</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -14150,11 +14150,11 @@
         </is>
       </c>
       <c r="H236">
-        <v>527</v>
+        <v>361</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311804164</t>
+          <t xml:space="preserve">311804163</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Kjeldsens Vej 44</t>
+          <t xml:space="preserve">Harald Leths Vej 2</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -14261,7 +14261,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">5715275</t>
+          <t xml:space="preserve">8064298</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -14270,11 +14270,11 @@
         </is>
       </c>
       <c r="H238">
-        <v>609</v>
+        <v>559</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311812175</t>
+          <t xml:space="preserve">311812166</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -14311,7 +14311,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vald Poulsens Vej 10</t>
+          <t xml:space="preserve">Niels Kjeldsens Vej 44</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -14321,7 +14321,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">5720630</t>
+          <t xml:space="preserve">5715275</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -14330,11 +14330,11 @@
         </is>
       </c>
       <c r="H239">
-        <v>562</v>
+        <v>609</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311812171</t>
+          <t xml:space="preserve">311812175</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harald Leths Vej 2</t>
+          <t xml:space="preserve">Parkvej 117</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -14381,7 +14381,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">8064298</t>
+          <t xml:space="preserve">8561221</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -14390,11 +14390,11 @@
         </is>
       </c>
       <c r="H240">
-        <v>559</v>
+        <v>589</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311812166</t>
+          <t xml:space="preserve">311812173</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 117</t>
+          <t xml:space="preserve">Vald Poulsens Vej 10</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">8561221</t>
+          <t xml:space="preserve">5720630</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -14450,11 +14450,11 @@
         </is>
       </c>
       <c r="H241">
-        <v>589</v>
+        <v>562</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311812173</t>
+          <t xml:space="preserve">311812171</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skjoldgården 52</t>
+          <t xml:space="preserve">Beethovensvej 12</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -14501,7 +14501,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">5713169</t>
+          <t xml:space="preserve">5718883</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -14510,11 +14510,11 @@
         </is>
       </c>
       <c r="H242">
-        <v>526</v>
+        <v>577</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813305</t>
+          <t xml:space="preserve">311813312</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -14551,7 +14551,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gårdhøjevej 5</t>
+          <t xml:space="preserve">Beethovensvej 12</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -14561,20 +14561,20 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">5717689</t>
+          <t xml:space="preserve">5718883</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H243">
-        <v>488</v>
+        <v>431</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813322</t>
+          <t xml:space="preserve">311813312</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wagnersvej 187</t>
+          <t xml:space="preserve">Gårdhøjevej 5</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -14621,7 +14621,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">5717893</t>
+          <t xml:space="preserve">5717689</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -14630,11 +14630,11 @@
         </is>
       </c>
       <c r="H244">
-        <v>1203</v>
+        <v>488</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813308</t>
+          <t xml:space="preserve">311813314</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -14671,7 +14671,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beethovensvej 12</t>
+          <t xml:space="preserve">Skjoldgården 52</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -14681,7 +14681,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">5718883</t>
+          <t xml:space="preserve">5713169</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -14690,11 +14690,11 @@
         </is>
       </c>
       <c r="H245">
-        <v>577</v>
+        <v>526</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813312</t>
+          <t xml:space="preserve">311813305</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beethovensvej 12</t>
+          <t xml:space="preserve">Wagnersvej 187</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -14741,20 +14741,20 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">5718883</t>
+          <t xml:space="preserve">5717893</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H246">
-        <v>431</v>
+        <v>1203</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813312</t>
+          <t xml:space="preserve">311813308</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">

--- a/public/exports/29189927.xlsx
+++ b/public/exports/29189927.xlsx
@@ -8514,7 +8514,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046014</t>
+          <t xml:space="preserve">200046010</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">

--- a/public/exports/29189927.xlsx
+++ b/public/exports/29189927.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L251"/>
+  <dimension ref="A1:M251"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2044,10 +2209,15 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2104,10 +2274,15 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2164,10 +2339,15 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2224,10 +2404,15 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2284,10 +2469,15 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2344,10 +2534,15 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2404,10 +2599,15 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2464,10 +2664,15 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2524,10 +2729,15 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2584,10 +2794,15 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2644,10 +2859,15 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2704,10 +2924,15 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2764,10 +2989,15 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2824,10 +3054,15 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2884,10 +3119,15 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2944,10 +3184,15 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3004,10 +3249,15 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3064,10 +3314,15 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3124,10 +3379,15 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3184,10 +3444,15 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3244,10 +3509,15 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3304,10 +3574,15 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3364,10 +3639,15 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3424,10 +3704,15 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3484,10 +3769,15 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3544,10 +3834,15 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3604,10 +3899,15 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3664,10 +3964,15 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3724,10 +4029,15 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3784,10 +4094,15 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3844,10 +4159,15 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3904,10 +4224,15 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3964,10 +4289,15 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4024,10 +4354,15 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4084,10 +4419,15 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4144,10 +4484,15 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4204,10 +4549,15 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4264,10 +4614,15 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4324,10 +4679,15 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4384,10 +4744,15 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4444,10 +4809,15 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4504,10 +4874,15 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4564,10 +4939,15 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4624,10 +5004,15 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4684,10 +5069,15 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4744,10 +5134,15 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4804,10 +5199,15 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4864,10 +5264,15 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4924,10 +5329,15 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4984,10 +5394,15 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5044,10 +5459,15 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5104,10 +5524,15 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5164,10 +5589,15 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5224,10 +5654,15 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5284,10 +5719,15 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5344,10 +5784,15 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5404,10 +5849,15 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5464,10 +5914,15 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5524,10 +5979,15 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5584,10 +6044,15 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5644,10 +6109,15 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5704,10 +6174,15 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5764,10 +6239,15 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5824,10 +6304,15 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5884,10 +6369,15 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5944,10 +6434,15 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6004,10 +6499,15 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6064,10 +6564,15 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6124,10 +6629,15 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6184,10 +6694,15 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6244,10 +6759,15 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6304,10 +6824,15 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6364,10 +6889,15 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6424,10 +6954,15 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6484,10 +7019,15 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6544,10 +7084,15 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6604,10 +7149,15 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6664,10 +7214,15 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6724,10 +7279,15 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6784,10 +7344,15 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6844,10 +7409,15 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6904,10 +7474,15 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6964,10 +7539,15 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7024,10 +7604,15 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7084,10 +7669,15 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7144,10 +7734,15 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7204,10 +7799,15 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7264,10 +7864,15 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7324,10 +7929,15 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">Enervice A/S</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-05-06</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
+      <c r="L123" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">Scanenergi A/S</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-09</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
+      <c r="L124" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">Scanenergi A/S</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-10</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
+      <c r="L125" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">Scanenergi A/S</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-16</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
+      <c r="L126" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr">
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">Scanenergi A/S</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-28</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
+      <c r="L127" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">Scanenergi A/S</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-11</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
+      <c r="L128" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr">
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">Scanenergi A/S</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-11</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
+      <c r="L129" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">Scanenergi A/S</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-16</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
+      <c r="L130" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">Scanenergi A/S</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
+      <c r="L131" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">Scanenergi A/S</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
+      <c r="L132" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr">
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-09-23</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
+      <c r="L133" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Holstebro)</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-01-27</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
+      <c r="L134" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-01-27</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
+      <c r="L135" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-23</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
+      <c r="L136" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-23</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
+      <c r="L137" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-23</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
+      <c r="L138" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr">
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-23</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
+      <c r="L139" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr">
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-23</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
+      <c r="L140" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr">
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-23</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
+      <c r="L141" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-23</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
+      <c r="L142" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-23</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
+      <c r="L143" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr">
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-23</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
+      <c r="L144" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr">
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-25</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
+      <c r="L145" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr">
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-25</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
+      <c r="L146" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr">
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-25</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
+      <c r="L147" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr">
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-25</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
+      <c r="L148" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Viborg)</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-25</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
+      <c r="L149" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr">
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-28</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
+      <c r="L150" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-08</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
+      <c r="L151" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr">
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-15</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
+      <c r="L152" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr">
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-15</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
+      <c r="L153" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr">
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-16</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
+      <c r="L154" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr">
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-16</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
+      <c r="L155" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr">
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-16</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
+      <c r="L156" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr">
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-16</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
+      <c r="L157" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-16</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
+      <c r="L158" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr">
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-16</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
+      <c r="L159" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr">
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-16</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
+      <c r="L160" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr">
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-16</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
+      <c r="L161" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr">
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-16</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
+      <c r="L162" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr">
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-16</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
+      <c r="L163" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-17</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
+      <c r="L164" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr">
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-17</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
+      <c r="L165" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr">
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-17</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
+      <c r="L166" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr">
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-17</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
+      <c r="L167" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr">
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-17</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
+      <c r="L168" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-17</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
+      <c r="L169" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr">
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-17</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
+      <c r="L170" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr">
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-17</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
+      <c r="L171" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr">
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-18</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
+      <c r="L172" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr">
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-18</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
+      <c r="L173" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr">
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-18</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
+      <c r="L174" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-18</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
+      <c r="L175" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-18</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
+      <c r="L176" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr">
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-18</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
+      <c r="L177" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr">
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-18</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
+      <c r="L178" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr">
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-18</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
+      <c r="L179" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr">
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-18</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
+      <c r="L180" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr">
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-18</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
+      <c r="L181" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr">
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-18</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
+      <c r="L182" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-18</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
+      <c r="L183" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr">
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-18</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
+      <c r="L184" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr">
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-29</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
+      <c r="L185" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr">
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-29</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
+      <c r="L186" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr">
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-30</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
+      <c r="L187" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr">
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-30</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
+      <c r="L188" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr">
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-30</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
+      <c r="L189" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L189" t="inlineStr">
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-30</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
+      <c r="L190" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L190" t="inlineStr">
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-30</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
+      <c r="L191" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L191" t="inlineStr">
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Holstebro)</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-09-02</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
+      <c r="L192" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr">
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-10-07</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
+      <c r="L193" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr">
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-10-07</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
+      <c r="L194" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L194" t="inlineStr">
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-10-11</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
+      <c r="L195" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr">
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-10-11</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
+      <c r="L196" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L196" t="inlineStr">
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11819,15 +12799,20 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-10-11</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
+      <c r="L197" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr">
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11879,15 +12864,20 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-10-13</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
+      <c r="L198" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr">
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11939,15 +12929,20 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-10-18</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
+      <c r="L199" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr">
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11999,15 +12994,20 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-10-24</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
+      <c r="L200" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr">
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -12059,15 +13059,20 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-10-24</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
+      <c r="L201" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr">
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -12119,15 +13124,20 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Holstebro - Holstebro Arkitektkontor ApS</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-11-01</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
+      <c r="L202" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr">
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -12179,15 +13189,20 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-11-07</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
+      <c r="L203" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L203" t="inlineStr">
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -12239,15 +13254,20 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-11-16</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
+      <c r="L204" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr">
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -12299,15 +13319,20 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Holstebro - Holstebro Arkitektkontor ApS</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-11-21</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
+      <c r="L205" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr">
+      <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -12359,15 +13384,20 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-01</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
+      <c r="L206" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr">
+      <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -12419,15 +13449,20 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-01</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
+      <c r="L207" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr">
+      <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -12479,15 +13514,20 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-01</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
+      <c r="L208" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr">
+      <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -12539,15 +13579,20 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-01</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
+      <c r="L209" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr">
+      <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -12599,15 +13644,20 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-03-22</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
+      <c r="L210" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr">
+      <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -12659,15 +13709,20 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
+          <t xml:space="preserve">Korsbæk &amp; Partnere Rådgivende ingeniørfirma KS</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-05-21</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
+      <c r="L211" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr">
+      <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -12719,15 +13774,20 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Kongens Lyngby)</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-12-10</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
+      <c r="L212" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L212" t="inlineStr">
+      <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -12779,15 +13839,20 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-12-11</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
+      <c r="L213" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr">
+      <c r="M213" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -12839,15 +13904,20 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-12-11</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
+      <c r="L214" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr">
+      <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -12899,15 +13969,20 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-04-16</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
+      <c r="L215" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr">
+      <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -12959,15 +14034,20 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
+          <t xml:space="preserve">KHBConsult</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-01-16</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
+      <c r="L216" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr">
+      <c r="M216" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -13019,15 +14099,20 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
+          <t xml:space="preserve">KHBConsult</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-01-16</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
+      <c r="L217" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L217" t="inlineStr">
+      <c r="M217" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -13079,15 +14164,20 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
+          <t xml:space="preserve">KHBConsult</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-08-22</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
+      <c r="L218" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L218" t="inlineStr">
+      <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -13139,15 +14229,20 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Center Midt- og Vestjylland</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-13</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
+      <c r="L219" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr">
+      <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -13199,15 +14294,20 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
+          <t xml:space="preserve">factum2 as</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-07-20</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
+      <c r="L220" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L220" t="inlineStr">
+      <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -13259,15 +14359,20 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
+          <t xml:space="preserve">KHB Consult</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-28</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
+      <c r="L221" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L221" t="inlineStr">
+      <c r="M221" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13319,15 +14424,20 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vest Consult v/Emanuel Laursen ApS</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-30</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
+      <c r="L222" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L222" t="inlineStr">
+      <c r="M222" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13379,15 +14489,20 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Center Midt- og Vestjylland</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
+      <c r="L223" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr">
+      <c r="M223" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13439,15 +14554,20 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-02</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
+      <c r="L224" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr">
+      <c r="M224" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13499,15 +14619,20 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-16</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
+      <c r="L225" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L225" t="inlineStr">
+      <c r="M225" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13559,15 +14684,20 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-16</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
+      <c r="L226" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr">
+      <c r="M226" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13619,15 +14749,20 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-16</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
+      <c r="L227" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L227" t="inlineStr">
+      <c r="M227" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13679,15 +14814,20 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-16</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
+      <c r="L228" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L228" t="inlineStr">
+      <c r="M228" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13739,15 +14879,20 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-29</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
+      <c r="L229" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L229" t="inlineStr">
+      <c r="M229" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13799,15 +14944,20 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-21</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
+      <c r="L230" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L230" t="inlineStr">
+      <c r="M230" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13859,15 +15009,20 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-28</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
+      <c r="L231" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L231" t="inlineStr">
+      <c r="M231" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13919,15 +15074,20 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-22</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
+      <c r="L232" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L232" t="inlineStr">
+      <c r="M232" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13979,15 +15139,20 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-22</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
+      <c r="L233" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L233" t="inlineStr">
+      <c r="M233" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14039,15 +15204,20 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-23</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr">
+      <c r="L234" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L234" t="inlineStr">
+      <c r="M234" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14099,15 +15269,20 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-23</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
+      <c r="L235" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L235" t="inlineStr">
+      <c r="M235" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14159,15 +15334,20 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-23</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr">
+      <c r="L236" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L236" t="inlineStr">
+      <c r="M236" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14219,15 +15399,20 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-17</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
+      <c r="L237" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L237" t="inlineStr">
+      <c r="M237" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14279,15 +15464,20 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-18</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
+      <c r="L238" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L238" t="inlineStr">
+      <c r="M238" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14339,15 +15529,20 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-18</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
+      <c r="L239" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L239" t="inlineStr">
+      <c r="M239" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14399,15 +15594,20 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-18</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
+      <c r="L240" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L240" t="inlineStr">
+      <c r="M240" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14459,15 +15659,20 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-18</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr">
+      <c r="L241" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L241" t="inlineStr">
+      <c r="M241" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14519,15 +15724,20 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-21</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr">
+      <c r="L242" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L242" t="inlineStr">
+      <c r="M242" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14579,15 +15789,20 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-21</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
+      <c r="L243" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L243" t="inlineStr">
+      <c r="M243" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14634,20 +15849,25 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813314</t>
+          <t xml:space="preserve">311813322</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-21</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr">
+      <c r="L244" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L244" t="inlineStr">
+      <c r="M244" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14699,15 +15919,20 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-21</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr">
+      <c r="L245" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L245" t="inlineStr">
+      <c r="M245" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14759,15 +15984,20 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-21</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr">
+      <c r="L246" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L246" t="inlineStr">
+      <c r="M246" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14819,15 +16049,20 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-01</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr">
+      <c r="L247" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L247" t="inlineStr">
+      <c r="M247" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14879,15 +16114,20 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-01</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr">
+      <c r="L248" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L248" t="inlineStr">
+      <c r="M248" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14939,15 +16179,20 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-26</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr">
+      <c r="L249" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L249" t="inlineStr">
+      <c r="M249" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14999,15 +16244,20 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-18</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr">
+      <c r="L250" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L250" t="inlineStr">
+      <c r="M250" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15059,21 +16309,26 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi &amp; Byg</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
+      <c r="L251" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr">
+      <c r="M251" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L251"/>
+  <autoFilter ref="A1:M251"/>
 </worksheet>
 </file>
--- a/public/exports/29189927.xlsx
+++ b/public/exports/29189927.xlsx
@@ -15849,7 +15849,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813322</t>
+          <t xml:space="preserve">311813314</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
